--- a/results/01_pollution_assessment/PCA_Stressors/tables/SumRel_site_rankings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/SumRel_site_rankings.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.267377728946281</v>
+        <v>-8.408446420325575</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,11 +467,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.41959144276309</v>
+        <v>-7.725635886671434</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.480325127657849</v>
+        <v>-7.070798260144645</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.497984556247476</v>
+        <v>-6.778211155027427</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -515,11 +515,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.53799541057551</v>
+        <v>-6.741788513807014</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -531,11 +531,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.587931943698385</v>
+        <v>-6.362828033611818</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -547,11 +547,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.592799680919376</v>
+        <v>-6.174750117083084</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -563,11 +563,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.599903870452274</v>
+        <v>-5.553535141554088</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -579,11 +579,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.635376515132371</v>
+        <v>-5.540141319681264</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -595,11 +595,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.655355032934677</v>
+        <v>-5.500124405885619</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -611,11 +611,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.65972121560007</v>
+        <v>-5.483087435645127</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -627,11 +627,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.68255615038818</v>
+        <v>-5.396011949673879</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -643,11 +643,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.686067623874442</v>
+        <v>-5.237198041119201</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -659,11 +659,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.6956326448348</v>
+        <v>-5.079209148699513</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>011A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.697702529447634</v>
+        <v>-5.073722926814928</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.699146526632239</v>
+        <v>-5.013805361332571</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -707,11 +707,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.712674570899483</v>
+        <v>-4.772390429294679</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -723,11 +723,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.719081411373789</v>
+        <v>-4.761208666495961</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -739,11 +739,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.720354307325032</v>
+        <v>-4.737479367004358</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -755,11 +755,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.729839265233774</v>
+        <v>-4.684564678614713</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -771,11 +771,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.740118668200615</v>
+        <v>-4.658442564146924</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -787,11 +787,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.749005322801854</v>
+        <v>-4.608611178408557</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -803,11 +803,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>030ABC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.749691462066005</v>
+        <v>-4.460906369824355</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
@@ -819,11 +819,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>035C</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.757680422973135</v>
+        <v>-4.371754731039946</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -835,11 +835,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.765264470594877</v>
+        <v>-4.343014940753482</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
@@ -851,11 +851,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.77136061975014</v>
+        <v>-4.321082271304928</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
@@ -867,11 +867,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>026C</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.781367992902675</v>
+        <v>-4.272209105059333</v>
       </c>
       <c r="D28" t="n">
         <v>27</v>
@@ -883,11 +883,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.814015012552385</v>
+        <v>-4.167533325162018</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
@@ -899,11 +899,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.814424290990326</v>
+        <v>-4.07490517685218</v>
       </c>
       <c r="D30" t="n">
         <v>29</v>
@@ -915,11 +915,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>016C</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.819100764139649</v>
+        <v>-3.988247202572773</v>
       </c>
       <c r="D31" t="n">
         <v>30</v>
@@ -931,11 +931,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.823652537543815</v>
+        <v>-3.889828156598327</v>
       </c>
       <c r="D32" t="n">
         <v>31</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>036C</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.8264396881881</v>
+        <v>-3.811657723467916</v>
       </c>
       <c r="D33" t="n">
         <v>32</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.83509232946154</v>
+        <v>-3.717841578324646</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -979,11 +979,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.840548077590976</v>
+        <v>-3.715428586207918</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>010B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.850380323804276</v>
+        <v>-3.520837853182157</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.855289598793966</v>
+        <v>-3.511872845967301</v>
       </c>
       <c r="D37" t="n">
         <v>36</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>S69</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.856580591721243</v>
+        <v>-3.492970868503443</v>
       </c>
       <c r="D38" t="n">
         <v>37</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.863250632167729</v>
+        <v>-3.488805848607047</v>
       </c>
       <c r="D39" t="n">
         <v>38</v>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>033ABC</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.864533266905906</v>
+        <v>-3.469077873800404</v>
       </c>
       <c r="D40" t="n">
         <v>39</v>
@@ -1075,11 +1075,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.874231056252467</v>
+        <v>-3.44340823541801</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.882490492086886</v>
+        <v>-3.442835751363971</v>
       </c>
       <c r="D42" t="n">
         <v>41</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.887965471466098</v>
+        <v>-3.407429351003314</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S74</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.921488818329889</v>
+        <v>-3.403153757934198</v>
       </c>
       <c r="D44" t="n">
         <v>43</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.922656049092005</v>
+        <v>-3.390807958478919</v>
       </c>
       <c r="D45" t="n">
         <v>44</v>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.924241807834034</v>
+        <v>-3.369951196409021</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>S79</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.940391299795311</v>
+        <v>-3.197326905102055</v>
       </c>
       <c r="D47" t="n">
         <v>46</v>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.941847447874568</v>
+        <v>-3.105183080734665</v>
       </c>
       <c r="D48" t="n">
         <v>47</v>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.946022617128232</v>
+        <v>-3.097435129452078</v>
       </c>
       <c r="D49" t="n">
         <v>48</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.946827249585245</v>
+        <v>-2.943030371468932</v>
       </c>
       <c r="D50" t="n">
         <v>49</v>
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.956132481892578</v>
+        <v>-2.937123789132318</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>023C</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.95637328929545</v>
+        <v>-2.892293824586156</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
@@ -1267,11 +1267,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>043ABC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.956837125037536</v>
+        <v>-2.847911773902649</v>
       </c>
       <c r="D53" t="n">
         <v>52</v>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>132B</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.958286583401054</v>
+        <v>-2.803518631798412</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t xml:space="preserve">111C </t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.962270156315282</v>
+        <v>-2.736934758958617</v>
       </c>
       <c r="D55" t="n">
         <v>54</v>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.963913055496472</v>
+        <v>-2.725675969725589</v>
       </c>
       <c r="D56" t="n">
         <v>55</v>
@@ -1331,11 +1331,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.965573784935676</v>
+        <v>-2.714862562487662</v>
       </c>
       <c r="D57" t="n">
         <v>56</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>021B</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.96579890939884</v>
+        <v>-2.690711375038359</v>
       </c>
       <c r="D58" t="n">
         <v>57</v>
@@ -1363,11 +1363,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DCC2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.967550286873326</v>
+        <v>-2.62872177151895</v>
       </c>
       <c r="D59" t="n">
         <v>58</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>098C</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.969973419804847</v>
+        <v>-2.623554577665243</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>S82</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.974536741320473</v>
+        <v>-2.595523859756483</v>
       </c>
       <c r="D61" t="n">
         <v>60</v>
@@ -1411,11 +1411,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>005ABC</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.980061994995101</v>
+        <v>-2.590055957787667</v>
       </c>
       <c r="D62" t="n">
         <v>61</v>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>S68</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.98659095328797</v>
+        <v>-2.515371125758628</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.991911662371239</v>
+        <v>-2.452259554580081</v>
       </c>
       <c r="D64" t="n">
         <v>63</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.996299924242431</v>
+        <v>-2.42921844237597</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>065C</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.001663093756192</v>
+        <v>-2.419221336438251</v>
       </c>
       <c r="D66" t="n">
         <v>65</v>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.012724679396036</v>
+        <v>-2.373926352357026</v>
       </c>
       <c r="D67" t="n">
         <v>66</v>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S102</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.024602947540684</v>
+        <v>-2.362272290763432</v>
       </c>
       <c r="D68" t="n">
         <v>67</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.026284898920165</v>
+        <v>-2.303009552299881</v>
       </c>
       <c r="D69" t="n">
         <v>68</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>077B</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.030724447306778</v>
+        <v>-2.199009062104753</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S99</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2.034841982253901</v>
+        <v>-2.196524144506577</v>
       </c>
       <c r="D71" t="n">
         <v>70</v>
@@ -1571,11 +1571,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.035944702964898</v>
+        <v>-2.084325081663102</v>
       </c>
       <c r="D72" t="n">
         <v>71</v>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>018A</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.037910447379761</v>
+        <v>-1.958360581429966</v>
       </c>
       <c r="D73" t="n">
         <v>72</v>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.04393451113358</v>
+        <v>-1.95413718592532</v>
       </c>
       <c r="D74" t="n">
         <v>73</v>
@@ -1619,11 +1619,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.051094598265961</v>
+        <v>-1.951880747874681</v>
       </c>
       <c r="D75" t="n">
         <v>74</v>
@@ -1635,11 +1635,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>019B</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.0511564272528</v>
+        <v>-1.909665670453775</v>
       </c>
       <c r="D76" t="n">
         <v>75</v>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2.068065267196406</v>
+        <v>-1.877476821385235</v>
       </c>
       <c r="D77" t="n">
         <v>76</v>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S97</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2.074170629105309</v>
+        <v>-1.835080785735737</v>
       </c>
       <c r="D78" t="n">
         <v>77</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>025B</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.083872627006261</v>
+        <v>-1.82685415910784</v>
       </c>
       <c r="D79" t="n">
         <v>78</v>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2.084703800191285</v>
+        <v>-1.824027632520316</v>
       </c>
       <c r="D80" t="n">
         <v>79</v>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>097ABC</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.089634443137524</v>
+        <v>-1.823944452402387</v>
       </c>
       <c r="D81" t="n">
         <v>80</v>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>057C</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2.093114728459417</v>
+        <v>-1.823001420937693</v>
       </c>
       <c r="D82" t="n">
         <v>81</v>
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>S21(5)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2.093341844944755</v>
+        <v>-1.814725180468137</v>
       </c>
       <c r="D83" t="n">
         <v>82</v>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>141B</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2.096273428956862</v>
+        <v>-1.805517677955268</v>
       </c>
       <c r="D84" t="n">
         <v>83</v>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>S67</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2.09755666968094</v>
+        <v>-1.794265770959105</v>
       </c>
       <c r="D85" t="n">
         <v>84</v>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2.105429015772428</v>
+        <v>-1.779455739569749</v>
       </c>
       <c r="D86" t="n">
         <v>85</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.111122281755686</v>
+        <v>-1.777424859779718</v>
       </c>
       <c r="D87" t="n">
         <v>86</v>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2.112084856300919</v>
+        <v>-1.609659841839567</v>
       </c>
       <c r="D88" t="n">
         <v>87</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>119B</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2.114976731832695</v>
+        <v>-1.563096644892145</v>
       </c>
       <c r="D89" t="n">
         <v>88</v>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>150B</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2.122204256854241</v>
+        <v>-1.551613653556252</v>
       </c>
       <c r="D90" t="n">
         <v>89</v>
@@ -1875,11 +1875,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2.124942249194262</v>
+        <v>-1.51644859239429</v>
       </c>
       <c r="D91" t="n">
         <v>90</v>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>S101</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2.133680624276793</v>
+        <v>-1.512867367598533</v>
       </c>
       <c r="D92" t="n">
         <v>91</v>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>117ABC</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2.136736479757284</v>
+        <v>-1.487773073915992</v>
       </c>
       <c r="D93" t="n">
         <v>92</v>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>078B</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2.142038247198994</v>
+        <v>-1.431373033692708</v>
       </c>
       <c r="D94" t="n">
         <v>93</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>S96</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2.1447348528261</v>
+        <v>-1.413816361382615</v>
       </c>
       <c r="D95" t="n">
         <v>94</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2.156624834714633</v>
+        <v>-1.385232343286459</v>
       </c>
       <c r="D96" t="n">
         <v>95</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2.160574503947267</v>
+        <v>-1.340488879451949</v>
       </c>
       <c r="D97" t="n">
         <v>96</v>
@@ -1987,11 +1987,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>S58</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2.166586058617908</v>
+        <v>-1.326510085021902</v>
       </c>
       <c r="D98" t="n">
         <v>97</v>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2.166886998732811</v>
+        <v>-1.292753856928735</v>
       </c>
       <c r="D99" t="n">
         <v>98</v>
@@ -2019,11 +2019,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>137A</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2.167399578748308</v>
+        <v>-1.258835681307973</v>
       </c>
       <c r="D100" t="n">
         <v>99</v>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>S40</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2.170724858175055</v>
+        <v>-1.248329078356066</v>
       </c>
       <c r="D101" t="n">
         <v>100</v>
@@ -2051,11 +2051,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>149C</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2.179427979287093</v>
+        <v>-1.207607767963565</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2067,11 +2067,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2.189717478082502</v>
+        <v>-1.103028424496936</v>
       </c>
       <c r="D103" t="n">
         <v>102</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>042C</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2.190325534865725</v>
+        <v>-1.08541138615484</v>
       </c>
       <c r="D104" t="n">
         <v>103</v>
@@ -2099,11 +2099,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>008A</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2.197833998920958</v>
+        <v>-1.074535861518894</v>
       </c>
       <c r="D105" t="n">
         <v>104</v>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2.199079042961261</v>
+        <v>-1.04788679348545</v>
       </c>
       <c r="D106" t="n">
         <v>105</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2.19947907359759</v>
+        <v>-1.02148914591152</v>
       </c>
       <c r="D107" t="n">
         <v>106</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2.203189639917697</v>
+        <v>-0.998921866402808</v>
       </c>
       <c r="D108" t="n">
         <v>107</v>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>012A</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2.211204947752738</v>
+        <v>-0.9542043501775823</v>
       </c>
       <c r="D109" t="n">
         <v>108</v>
@@ -2179,11 +2179,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>127B</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2.213823646660722</v>
+        <v>-0.8886262767266497</v>
       </c>
       <c r="D110" t="n">
         <v>109</v>
@@ -2195,11 +2195,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>146B</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2.216673110272878</v>
+        <v>-0.7591545561766914</v>
       </c>
       <c r="D111" t="n">
         <v>110</v>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>114B</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2.223126384917812</v>
+        <v>-0.6935002249558597</v>
       </c>
       <c r="D112" t="n">
         <v>111</v>
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>S63</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2.223387786056885</v>
+        <v>-0.6819864824319706</v>
       </c>
       <c r="D113" t="n">
         <v>112</v>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>024C</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2.224478036930559</v>
+        <v>-0.6637302691957245</v>
       </c>
       <c r="D114" t="n">
         <v>113</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>143B</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2.226973269905113</v>
+        <v>-0.6457202724962933</v>
       </c>
       <c r="D115" t="n">
         <v>114</v>
@@ -2275,11 +2275,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2.231048248706692</v>
+        <v>-0.6131065608954915</v>
       </c>
       <c r="D116" t="n">
         <v>115</v>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>S66</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2.231248938150776</v>
+        <v>-0.6115133564953452</v>
       </c>
       <c r="D117" t="n">
         <v>116</v>
@@ -2307,11 +2307,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2.237451327282891</v>
+        <v>-0.5688762431227989</v>
       </c>
       <c r="D118" t="n">
         <v>117</v>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>115ABC</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2.249953539859346</v>
+        <v>-0.5123016982644781</v>
       </c>
       <c r="D119" t="n">
         <v>118</v>
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>102B</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2.258778160138382</v>
+        <v>-0.4591346569471696</v>
       </c>
       <c r="D120" t="n">
         <v>119</v>
@@ -2355,11 +2355,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>144B</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2.263291402362695</v>
+        <v>-0.4445858262261141</v>
       </c>
       <c r="D121" t="n">
         <v>120</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>A53</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2.276591213569075</v>
+        <v>-0.4295471535086562</v>
       </c>
       <c r="D122" t="n">
         <v>121</v>
@@ -2387,11 +2387,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2.280966722486821</v>
+        <v>-0.4136621005620263</v>
       </c>
       <c r="D123" t="n">
         <v>122</v>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>142C</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2.283687347209508</v>
+        <v>-0.4095655588128816</v>
       </c>
       <c r="D124" t="n">
         <v>123</v>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2.284717445377044</v>
+        <v>-0.4032446095993193</v>
       </c>
       <c r="D125" t="n">
         <v>124</v>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>072A</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2.286760865150849</v>
+        <v>-0.2374432786028324</v>
       </c>
       <c r="D126" t="n">
         <v>125</v>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2.291570420175599</v>
+        <v>-0.2265640866639765</v>
       </c>
       <c r="D127" t="n">
         <v>126</v>
@@ -2467,11 +2467,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>148B</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2.297202467234839</v>
+        <v>-0.2213021407340587</v>
       </c>
       <c r="D128" t="n">
         <v>127</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>116B</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2.306706400601063</v>
+        <v>-0.06628097554298429</v>
       </c>
       <c r="D129" t="n">
         <v>128</v>
@@ -2499,11 +2499,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2.306931397631996</v>
+        <v>-0.0504281816013018</v>
       </c>
       <c r="D130" t="n">
         <v>129</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2.317775570522614</v>
+        <v>0.06820622532727638</v>
       </c>
       <c r="D131" t="n">
         <v>130</v>
@@ -2531,11 +2531,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2.319169845368289</v>
+        <v>0.140095521734675</v>
       </c>
       <c r="D132" t="n">
         <v>131</v>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>129A</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2.322124876224269</v>
+        <v>0.172106207509748</v>
       </c>
       <c r="D133" t="n">
         <v>132</v>
@@ -2563,11 +2563,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S93</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2.326024631400954</v>
+        <v>0.1892484853217944</v>
       </c>
       <c r="D134" t="n">
         <v>133</v>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>S95</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2.326577164822367</v>
+        <v>0.2886403532412899</v>
       </c>
       <c r="D135" t="n">
         <v>134</v>
@@ -2595,11 +2595,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>S100</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2.327800757639896</v>
+        <v>0.3371140007776494</v>
       </c>
       <c r="D136" t="n">
         <v>135</v>
@@ -2611,11 +2611,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2.328425171511971</v>
+        <v>0.49324976933939</v>
       </c>
       <c r="D137" t="n">
         <v>136</v>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>070B</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2.332935920758041</v>
+        <v>0.5393268390483814</v>
       </c>
       <c r="D138" t="n">
         <v>137</v>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>009B</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2.342738156704757</v>
+        <v>0.5629463774175526</v>
       </c>
       <c r="D139" t="n">
         <v>138</v>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>067B</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2.347629236282947</v>
+        <v>0.5659713721060877</v>
       </c>
       <c r="D140" t="n">
         <v>139</v>
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2.353958206813392</v>
+        <v>0.5809868471088423</v>
       </c>
       <c r="D141" t="n">
         <v>140</v>
@@ -2691,11 +2691,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>013A</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2.354701135242428</v>
+        <v>0.6180088988186799</v>
       </c>
       <c r="D142" t="n">
         <v>141</v>
@@ -2707,11 +2707,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>S80</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2.355437518210778</v>
+        <v>0.7004643741638442</v>
       </c>
       <c r="D143" t="n">
         <v>142</v>
@@ -2723,11 +2723,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2.35742806758786</v>
+        <v>0.7308312681376758</v>
       </c>
       <c r="D144" t="n">
         <v>143</v>
@@ -2739,11 +2739,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S78</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2.360653385828175</v>
+        <v>0.7670161598215928</v>
       </c>
       <c r="D145" t="n">
         <v>144</v>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>130A</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2.362303663218555</v>
+        <v>0.8233755248822641</v>
       </c>
       <c r="D146" t="n">
         <v>145</v>
@@ -2771,11 +2771,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>045B</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2.365281800563952</v>
+        <v>0.9958979042348548</v>
       </c>
       <c r="D147" t="n">
         <v>146</v>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>069A</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2.366031854330265</v>
+        <v>1.023517559990041</v>
       </c>
       <c r="D148" t="n">
         <v>147</v>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2.371609573871898</v>
+        <v>1.084806202959793</v>
       </c>
       <c r="D149" t="n">
         <v>148</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2.382019409392692</v>
+        <v>1.202636293057992</v>
       </c>
       <c r="D150" t="n">
         <v>149</v>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>145B</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2.385773459994635</v>
+        <v>1.240720923818688</v>
       </c>
       <c r="D151" t="n">
         <v>150</v>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S46</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2.393307037852836</v>
+        <v>1.244740382922031</v>
       </c>
       <c r="D152" t="n">
         <v>151</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>034C</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2.395703430304021</v>
+        <v>1.306343721320207</v>
       </c>
       <c r="D153" t="n">
         <v>152</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>134C</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2.396291383950244</v>
+        <v>1.328586088250863</v>
       </c>
       <c r="D154" t="n">
         <v>153</v>
@@ -2899,11 +2899,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>118A</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2.416306192148566</v>
+        <v>1.422984192406221</v>
       </c>
       <c r="D155" t="n">
         <v>154</v>
@@ -2915,11 +2915,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>044A</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2.425967768448829</v>
+        <v>1.436691716346055</v>
       </c>
       <c r="D156" t="n">
         <v>155</v>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>105C</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2.428389608256134</v>
+        <v>1.441563767440232</v>
       </c>
       <c r="D157" t="n">
         <v>156</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>027B</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2.428769770649007</v>
+        <v>1.455724127258949</v>
       </c>
       <c r="D158" t="n">
         <v>157</v>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>075A</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2.435446972553423</v>
+        <v>1.528777531273058</v>
       </c>
       <c r="D159" t="n">
         <v>158</v>
@@ -2979,11 +2979,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2.445950551269787</v>
+        <v>1.561899450826634</v>
       </c>
       <c r="D160" t="n">
         <v>159</v>
@@ -2995,11 +2995,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>048C</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2.452046058937082</v>
+        <v>1.782955583519249</v>
       </c>
       <c r="D161" t="n">
         <v>160</v>
@@ -3011,11 +3011,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>047ABC</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2.453340523812644</v>
+        <v>1.789251504757831</v>
       </c>
       <c r="D162" t="n">
         <v>161</v>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2.455818527721652</v>
+        <v>1.79261628926828</v>
       </c>
       <c r="D163" t="n">
         <v>162</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>017B</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2.461721010099457</v>
+        <v>1.826986330455241</v>
       </c>
       <c r="D164" t="n">
         <v>163</v>
@@ -3059,11 +3059,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>014B</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2.467925848234416</v>
+        <v>1.890732861937404</v>
       </c>
       <c r="D165" t="n">
         <v>164</v>
@@ -3075,11 +3075,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>003ABC</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2.468161441532856</v>
+        <v>1.91479598779764</v>
       </c>
       <c r="D166" t="n">
         <v>165</v>
@@ -3091,11 +3091,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>136B</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2.483122943432949</v>
+        <v>1.988942573301032</v>
       </c>
       <c r="D167" t="n">
         <v>166</v>
@@ -3107,11 +3107,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>029C</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2.511844681103095</v>
+        <v>2.000314396412177</v>
       </c>
       <c r="D168" t="n">
         <v>167</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>054B</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2.513430666320724</v>
+        <v>2.062392479299338</v>
       </c>
       <c r="D169" t="n">
         <v>168</v>
@@ -3139,11 +3139,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>123A</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2.516058244911793</v>
+        <v>2.068315213778967</v>
       </c>
       <c r="D170" t="n">
         <v>169</v>
@@ -3155,11 +3155,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>107C</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2.521485384160801</v>
+        <v>2.179102466421639</v>
       </c>
       <c r="D171" t="n">
         <v>170</v>
@@ -3171,11 +3171,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>126A</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2.523457310390944</v>
+        <v>2.22878959637643</v>
       </c>
       <c r="D172" t="n">
         <v>171</v>
@@ -3187,11 +3187,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2.535023427331285</v>
+        <v>2.296253374541168</v>
       </c>
       <c r="D173" t="n">
         <v>172</v>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>022B</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2.536081467205239</v>
+        <v>2.310301702762307</v>
       </c>
       <c r="D174" t="n">
         <v>173</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>037B</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2.53630204743449</v>
+        <v>2.317656374873265</v>
       </c>
       <c r="D175" t="n">
         <v>174</v>
@@ -3235,11 +3235,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>080C</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2.538021683189385</v>
+        <v>2.368692299963941</v>
       </c>
       <c r="D176" t="n">
         <v>175</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>113B</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2.553916868025238</v>
+        <v>2.380171178330807</v>
       </c>
       <c r="D177" t="n">
         <v>176</v>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>131B</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2.564520295948148</v>
+        <v>2.443868694700753</v>
       </c>
       <c r="D178" t="n">
         <v>177</v>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>124A</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2.56513296321162</v>
+        <v>2.602352805827155</v>
       </c>
       <c r="D179" t="n">
         <v>178</v>
@@ -3299,11 +3299,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>106B</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2.567269894938152</v>
+        <v>2.632185626256154</v>
       </c>
       <c r="D180" t="n">
         <v>179</v>
@@ -3315,11 +3315,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>074B</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2.574249921944149</v>
+        <v>2.713722659289608</v>
       </c>
       <c r="D181" t="n">
         <v>180</v>
@@ -3331,11 +3331,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>103A</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2.575143254829423</v>
+        <v>2.724284957849016</v>
       </c>
       <c r="D182" t="n">
         <v>181</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>082A</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2.58173120276074</v>
+        <v>2.819258408382049</v>
       </c>
       <c r="D183" t="n">
         <v>182</v>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2.592087358193917</v>
+        <v>3.027344015601057</v>
       </c>
       <c r="D184" t="n">
         <v>183</v>
@@ -3379,11 +3379,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>095A</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2.613392401706197</v>
+        <v>3.033690895756802</v>
       </c>
       <c r="D185" t="n">
         <v>184</v>
@@ -3395,11 +3395,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>UCC1</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2.621673805581241</v>
+        <v>3.06241371478278</v>
       </c>
       <c r="D186" t="n">
         <v>185</v>
@@ -3411,11 +3411,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>135A</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2.623521679116926</v>
+        <v>3.111529434587468</v>
       </c>
       <c r="D187" t="n">
         <v>186</v>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>S87</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2.660090922031275</v>
+        <v>3.256061200682942</v>
       </c>
       <c r="D188" t="n">
         <v>187</v>
@@ -3443,11 +3443,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>128B</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2.66358572557284</v>
+        <v>3.257064140483741</v>
       </c>
       <c r="D189" t="n">
         <v>188</v>
@@ -3459,11 +3459,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>091C</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2.695410281693217</v>
+        <v>3.31807790391069</v>
       </c>
       <c r="D190" t="n">
         <v>189</v>
@@ -3475,11 +3475,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>UCE1</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2.697866645085115</v>
+        <v>3.365369660364951</v>
       </c>
       <c r="D191" t="n">
         <v>190</v>
@@ -3491,11 +3491,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>108B</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2.699515062297849</v>
+        <v>3.680379185734977</v>
       </c>
       <c r="D192" t="n">
         <v>191</v>
@@ -3507,11 +3507,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>A58</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2.706243498091828</v>
+        <v>3.771129961104986</v>
       </c>
       <c r="D193" t="n">
         <v>192</v>
@@ -3523,11 +3523,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>083B</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2.70764789314648</v>
+        <v>3.779758408874764</v>
       </c>
       <c r="D194" t="n">
         <v>193</v>
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>015C</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2.731266212506753</v>
+        <v>3.790973384713912</v>
       </c>
       <c r="D195" t="n">
         <v>194</v>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>138B</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2.76122785331315</v>
+        <v>3.797260880298193</v>
       </c>
       <c r="D196" t="n">
         <v>195</v>
@@ -3571,11 +3571,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>092ABC</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2.76175881376084</v>
+        <v>3.797628319046731</v>
       </c>
       <c r="D197" t="n">
         <v>196</v>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>049A</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2.767658466815638</v>
+        <v>3.835545877538793</v>
       </c>
       <c r="D198" t="n">
         <v>197</v>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>S94</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2.778773550497863</v>
+        <v>3.837458472037349</v>
       </c>
       <c r="D199" t="n">
         <v>198</v>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>140C</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2.784087022393352</v>
+        <v>4.095082947534874</v>
       </c>
       <c r="D200" t="n">
         <v>199</v>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>S83</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>2.80677906407145</v>
+        <v>4.102580822655615</v>
       </c>
       <c r="D201" t="n">
         <v>200</v>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>079C</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2.811599330696371</v>
+        <v>4.128308785060249</v>
       </c>
       <c r="D202" t="n">
         <v>201</v>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2.817942104020186</v>
+        <v>4.339156322456247</v>
       </c>
       <c r="D203" t="n">
         <v>202</v>
@@ -3683,11 +3683,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>UBC1</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2.81986200162722</v>
+        <v>4.359363378431035</v>
       </c>
       <c r="D204" t="n">
         <v>203</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2.824428254541614</v>
+        <v>4.522305970849448</v>
       </c>
       <c r="D205" t="n">
         <v>204</v>
@@ -3715,11 +3715,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DBC2</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2.850039865917742</v>
+        <v>4.582455343000344</v>
       </c>
       <c r="D206" t="n">
         <v>205</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2.857688738456741</v>
+        <v>4.70792757008001</v>
       </c>
       <c r="D207" t="n">
         <v>206</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DJC2</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2.878619916005815</v>
+        <v>4.743431511603315</v>
       </c>
       <c r="D208" t="n">
         <v>207</v>
@@ -3763,11 +3763,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>085C</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2.918917674077924</v>
+        <v>5.069724879076849</v>
       </c>
       <c r="D209" t="n">
         <v>208</v>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>UJC1</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2.926815662450544</v>
+        <v>5.219261352581796</v>
       </c>
       <c r="D210" t="n">
         <v>209</v>
@@ -3795,11 +3795,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>S89</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2.931375062218854</v>
+        <v>5.287726803825795</v>
       </c>
       <c r="D211" t="n">
         <v>210</v>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>090B</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2.954882287793785</v>
+        <v>5.410417555488351</v>
       </c>
       <c r="D212" t="n">
         <v>211</v>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>MCE2</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2.963178281022482</v>
+        <v>5.45440648523253</v>
       </c>
       <c r="D213" t="n">
         <v>212</v>
@@ -3843,11 +3843,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>147A</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2.966741635078163</v>
+        <v>5.480026990128871</v>
       </c>
       <c r="D214" t="n">
         <v>213</v>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2.974974154604542</v>
+        <v>5.528731378728785</v>
       </c>
       <c r="D215" t="n">
         <v>214</v>
@@ -3875,11 +3875,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2.98650154228345</v>
+        <v>5.616666174333869</v>
       </c>
       <c r="D216" t="n">
         <v>215</v>
@@ -3891,11 +3891,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>031A</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2.992297397362443</v>
+        <v>5.639862559627898</v>
       </c>
       <c r="D217" t="n">
         <v>216</v>
@@ -3907,11 +3907,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>059ABC</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3.007977987695615</v>
+        <v>5.903358574383061</v>
       </c>
       <c r="D218" t="n">
         <v>217</v>
@@ -3923,11 +3923,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>096A</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3.010180697508016</v>
+        <v>5.995475629364829</v>
       </c>
       <c r="D219" t="n">
         <v>218</v>
@@ -3939,11 +3939,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>099C</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3.035111321170719</v>
+        <v>6.061938958827319</v>
       </c>
       <c r="D220" t="n">
         <v>219</v>
@@ -3955,11 +3955,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>S85</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3.037279593619371</v>
+        <v>6.498998653210989</v>
       </c>
       <c r="D221" t="n">
         <v>220</v>
@@ -3971,11 +3971,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>076ABC</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3.052385339417484</v>
+        <v>6.877894116815751</v>
       </c>
       <c r="D222" t="n">
         <v>221</v>
@@ -3987,11 +3987,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>S90</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3.053044720706486</v>
+        <v>6.904748360547603</v>
       </c>
       <c r="D223" t="n">
         <v>222</v>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>S27(5)</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3.09275938411877</v>
+        <v>7.014331604878336</v>
       </c>
       <c r="D224" t="n">
         <v>223</v>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>084A</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>3.124744084394261</v>
+        <v>7.092194982282656</v>
       </c>
       <c r="D225" t="n">
         <v>224</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>086A</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3.132123317376894</v>
+        <v>7.255717804581041</v>
       </c>
       <c r="D226" t="n">
         <v>225</v>
@@ -4051,11 +4051,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>052B</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3.162325813413912</v>
+        <v>7.296760852853477</v>
       </c>
       <c r="D227" t="n">
         <v>226</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3.162333285011525</v>
+        <v>7.379207310869586</v>
       </c>
       <c r="D228" t="n">
         <v>227</v>
@@ -4083,11 +4083,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>007ABC</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>3.184684378727726</v>
+        <v>7.546725419494346</v>
       </c>
       <c r="D229" t="n">
         <v>228</v>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>081B</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3.213382159378861</v>
+        <v>7.692681901639905</v>
       </c>
       <c r="D230" t="n">
         <v>229</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3.218623461786999</v>
+        <v>7.956443995041351</v>
       </c>
       <c r="D231" t="n">
         <v>230</v>
@@ -4131,11 +4131,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>088C</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>3.232749633922047</v>
+        <v>8.355052443775538</v>
       </c>
       <c r="D232" t="n">
         <v>231</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>055C</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3.449796541904556</v>
+        <v>9.758422029443398</v>
       </c>
       <c r="D233" t="n">
         <v>232</v>
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>101C</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3.521954334390625</v>
+        <v>10.50503389945685</v>
       </c>
       <c r="D234" t="n">
         <v>233</v>

--- a/results/01_pollution_assessment/PCA_Stressors/tables/SumRel_site_rankings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/SumRel_site_rankings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D234"/>
+  <dimension ref="A1:D311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-8.408446420325575</v>
+        <v>0.8757009819408152</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,11 +467,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-7.725635886671434</v>
+        <v>0.9894938356146357</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-7.070798260144645</v>
+        <v>1.121643085678034</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-6.778211155027427</v>
+        <v>1.14091151471174</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -515,11 +515,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-6.741788513807014</v>
+        <v>1.178571299416075</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -531,11 +531,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-6.362828033611818</v>
+        <v>1.188744169565138</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -547,11 +547,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-6.174750117083084</v>
+        <v>1.197514984370817</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -563,11 +563,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-5.553535141554088</v>
+        <v>1.203952743873251</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -579,11 +579,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-5.540141319681264</v>
+        <v>1.211641528286106</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -595,11 +595,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-5.500124405885619</v>
+        <v>1.241038451205754</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -611,11 +611,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-5.483087435645127</v>
+        <v>1.257063412161886</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -627,11 +627,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-5.396011949673879</v>
+        <v>1.292101778402669</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -643,11 +643,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-5.237198041119201</v>
+        <v>1.313871199859042</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -659,11 +659,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-5.079209148699513</v>
+        <v>1.328582602333761</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-5.073722926814928</v>
+        <v>1.353105389684064</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-5.013805361332571</v>
+        <v>1.362206860533212</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -707,11 +707,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-4.772390429294679</v>
+        <v>1.366378450025826</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -723,11 +723,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-4.761208666495961</v>
+        <v>1.390860702083689</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -739,11 +739,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-4.737479367004358</v>
+        <v>1.393934924195571</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -755,11 +755,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-4.684564678614713</v>
+        <v>1.398359703675624</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -771,11 +771,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-4.658442564146924</v>
+        <v>1.417547588632952</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -787,11 +787,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-4.608611178408557</v>
+        <v>1.424180086333783</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -803,11 +803,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-4.460906369824355</v>
+        <v>1.440067743901287</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
@@ -819,11 +819,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-4.371754731039946</v>
+        <v>1.442066646114398</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -835,11 +835,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-4.343014940753482</v>
+        <v>1.451848181104439</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
@@ -851,11 +851,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-4.321082271304928</v>
+        <v>1.467481933616187</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
@@ -867,11 +867,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-4.272209105059333</v>
+        <v>1.478471109682633</v>
       </c>
       <c r="D28" t="n">
         <v>27</v>
@@ -883,11 +883,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-4.167533325162018</v>
+        <v>1.486661628571753</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
@@ -899,11 +899,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-4.07490517685218</v>
+        <v>1.486668689272614</v>
       </c>
       <c r="D30" t="n">
         <v>29</v>
@@ -915,11 +915,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-3.988247202572773</v>
+        <v>1.495126099100238</v>
       </c>
       <c r="D31" t="n">
         <v>30</v>
@@ -931,11 +931,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-3.889828156598327</v>
+        <v>1.49812549377652</v>
       </c>
       <c r="D32" t="n">
         <v>31</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-3.811657723467916</v>
+        <v>1.500963200559916</v>
       </c>
       <c r="D33" t="n">
         <v>32</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-3.717841578324646</v>
+        <v>1.503430985927214</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -979,11 +979,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-3.715428586207918</v>
+        <v>1.503540936109761</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-3.520837853182157</v>
+        <v>1.505515821228682</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-3.511872845967301</v>
+        <v>1.508165646919392</v>
       </c>
       <c r="D37" t="n">
         <v>36</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-3.492970868503443</v>
+        <v>1.518525973087024</v>
       </c>
       <c r="D38" t="n">
         <v>37</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-3.488805848607047</v>
+        <v>1.518811354151904</v>
       </c>
       <c r="D39" t="n">
         <v>38</v>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-3.469077873800404</v>
+        <v>1.520808695996315</v>
       </c>
       <c r="D40" t="n">
         <v>39</v>
@@ -1075,11 +1075,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-3.44340823541801</v>
+        <v>1.524349086095014</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-3.442835751363971</v>
+        <v>1.528140502565595</v>
       </c>
       <c r="D42" t="n">
         <v>41</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-3.407429351003314</v>
+        <v>1.53368466317342</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-3.403153757934198</v>
+        <v>1.569334203393288</v>
       </c>
       <c r="D44" t="n">
         <v>43</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-3.390807958478919</v>
+        <v>1.570481963046426</v>
       </c>
       <c r="D45" t="n">
         <v>44</v>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.369951196409021</v>
+        <v>1.57142651631452</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-3.197326905102055</v>
+        <v>1.573282739034406</v>
       </c>
       <c r="D47" t="n">
         <v>46</v>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-3.105183080734665</v>
+        <v>1.575922144773402</v>
       </c>
       <c r="D48" t="n">
         <v>47</v>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-3.097435129452078</v>
+        <v>1.579754808826731</v>
       </c>
       <c r="D49" t="n">
         <v>48</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-2.943030371468932</v>
+        <v>1.581937322093751</v>
       </c>
       <c r="D50" t="n">
         <v>49</v>
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2.937123789132318</v>
+        <v>1.585509022662273</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-2.892293824586156</v>
+        <v>1.590503873146879</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
@@ -1267,11 +1267,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-2.847911773902649</v>
+        <v>1.590615617364291</v>
       </c>
       <c r="D53" t="n">
         <v>52</v>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-2.803518631798412</v>
+        <v>1.592123527375639</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-2.736934758958617</v>
+        <v>1.592457738419646</v>
       </c>
       <c r="D55" t="n">
         <v>54</v>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-2.725675969725589</v>
+        <v>1.592805311151601</v>
       </c>
       <c r="D56" t="n">
         <v>55</v>
@@ -1331,11 +1331,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-2.714862562487662</v>
+        <v>1.59590103954848</v>
       </c>
       <c r="D57" t="n">
         <v>56</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-2.690711375038359</v>
+        <v>1.602339029925951</v>
       </c>
       <c r="D58" t="n">
         <v>57</v>
@@ -1363,11 +1363,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-148</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-2.62872177151895</v>
+        <v>1.603465383395154</v>
       </c>
       <c r="D59" t="n">
         <v>58</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-2.623554577665243</v>
+        <v>1.611302977050177</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-2.595523859756483</v>
+        <v>1.615587549238018</v>
       </c>
       <c r="D61" t="n">
         <v>60</v>
@@ -1411,11 +1411,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-2.590055957787667</v>
+        <v>1.615607344736268</v>
       </c>
       <c r="D62" t="n">
         <v>61</v>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-2.515371125758628</v>
+        <v>1.623760967257978</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-2.452259554580081</v>
+        <v>1.626778857386204</v>
       </c>
       <c r="D64" t="n">
         <v>63</v>
@@ -1459,11 +1459,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-2.42921844237597</v>
+        <v>1.62830561492514</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2.419221336438251</v>
+        <v>1.635113606183217</v>
       </c>
       <c r="D66" t="n">
         <v>65</v>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-2.373926352357026</v>
+        <v>1.639617844905057</v>
       </c>
       <c r="D67" t="n">
         <v>66</v>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-2.362272290763432</v>
+        <v>1.642962111862984</v>
       </c>
       <c r="D68" t="n">
         <v>67</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-2.303009552299881</v>
+        <v>1.648942604025713</v>
       </c>
       <c r="D69" t="n">
         <v>68</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-2.199009062104753</v>
+        <v>1.657598486022446</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-2.196524144506577</v>
+        <v>1.661334682760783</v>
       </c>
       <c r="D71" t="n">
         <v>70</v>
@@ -1571,11 +1571,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-2.084325081663102</v>
+        <v>1.662046313159057</v>
       </c>
       <c r="D72" t="n">
         <v>71</v>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-1.958360581429966</v>
+        <v>1.666514154770887</v>
       </c>
       <c r="D73" t="n">
         <v>72</v>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1.95413718592532</v>
+        <v>1.66779747306475</v>
       </c>
       <c r="D74" t="n">
         <v>73</v>
@@ -1619,11 +1619,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1.951880747874681</v>
+        <v>1.668352233211897</v>
       </c>
       <c r="D75" t="n">
         <v>74</v>
@@ -1635,11 +1635,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1.909665670453775</v>
+        <v>1.670382642350369</v>
       </c>
       <c r="D76" t="n">
         <v>75</v>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1.877476821385235</v>
+        <v>1.6711609754695</v>
       </c>
       <c r="D77" t="n">
         <v>76</v>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1.835080785735737</v>
+        <v>1.674647114460876</v>
       </c>
       <c r="D78" t="n">
         <v>77</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1.82685415910784</v>
+        <v>1.674982653951614</v>
       </c>
       <c r="D79" t="n">
         <v>78</v>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-1.824027632520316</v>
+        <v>1.678923181244775</v>
       </c>
       <c r="D80" t="n">
         <v>79</v>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1.823944452402387</v>
+        <v>1.680035042257388</v>
       </c>
       <c r="D81" t="n">
         <v>80</v>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-152</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1.823001420937693</v>
+        <v>1.681065236127189</v>
       </c>
       <c r="D82" t="n">
         <v>81</v>
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1.814725180468137</v>
+        <v>1.681199253639464</v>
       </c>
       <c r="D83" t="n">
         <v>82</v>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-1.805517677955268</v>
+        <v>1.684072709393042</v>
       </c>
       <c r="D84" t="n">
         <v>83</v>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1.794265770959105</v>
+        <v>1.692057886931791</v>
       </c>
       <c r="D85" t="n">
         <v>84</v>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-1.779455739569749</v>
+        <v>1.692311346145622</v>
       </c>
       <c r="D86" t="n">
         <v>85</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1.777424859779718</v>
+        <v>1.703848510508728</v>
       </c>
       <c r="D87" t="n">
         <v>86</v>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1.609659841839567</v>
+        <v>1.711075856795166</v>
       </c>
       <c r="D88" t="n">
         <v>87</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-1.563096644892145</v>
+        <v>1.71183269889984</v>
       </c>
       <c r="D89" t="n">
         <v>88</v>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-1.551613653556252</v>
+        <v>1.717817283583649</v>
       </c>
       <c r="D90" t="n">
         <v>89</v>
@@ -1875,11 +1875,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-1.51644859239429</v>
+        <v>1.71851742253445</v>
       </c>
       <c r="D91" t="n">
         <v>90</v>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-1.512867367598533</v>
+        <v>1.720956427424588</v>
       </c>
       <c r="D92" t="n">
         <v>91</v>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-1.487773073915992</v>
+        <v>1.727615666239964</v>
       </c>
       <c r="D93" t="n">
         <v>92</v>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1.431373033692708</v>
+        <v>1.728831537770571</v>
       </c>
       <c r="D94" t="n">
         <v>93</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-1.413816361382615</v>
+        <v>1.731079539231763</v>
       </c>
       <c r="D95" t="n">
         <v>94</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1.385232343286459</v>
+        <v>1.736811572256539</v>
       </c>
       <c r="D96" t="n">
         <v>95</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-1.340488879451949</v>
+        <v>1.738954699200735</v>
       </c>
       <c r="D97" t="n">
         <v>96</v>
@@ -1987,11 +1987,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1.326510085021902</v>
+        <v>1.741515462795688</v>
       </c>
       <c r="D98" t="n">
         <v>97</v>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-1.292753856928735</v>
+        <v>1.749234351293034</v>
       </c>
       <c r="D99" t="n">
         <v>98</v>
@@ -2019,11 +2019,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-1.258835681307973</v>
+        <v>1.756042382798823</v>
       </c>
       <c r="D100" t="n">
         <v>99</v>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-1.248329078356066</v>
+        <v>1.761085045435297</v>
       </c>
       <c r="D101" t="n">
         <v>100</v>
@@ -2051,11 +2051,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-1.207607767963565</v>
+        <v>1.764420820455963</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2067,11 +2067,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-1.103028424496936</v>
+        <v>1.766646081349474</v>
       </c>
       <c r="D103" t="n">
         <v>102</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-1.08541138615484</v>
+        <v>1.776910899095918</v>
       </c>
       <c r="D104" t="n">
         <v>103</v>
@@ -2099,11 +2099,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-1.074535861518894</v>
+        <v>1.777415381980655</v>
       </c>
       <c r="D105" t="n">
         <v>104</v>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-1.04788679348545</v>
+        <v>1.782061461074954</v>
       </c>
       <c r="D106" t="n">
         <v>105</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-1.02148914591152</v>
+        <v>1.783649164944135</v>
       </c>
       <c r="D107" t="n">
         <v>106</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-151</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-0.998921866402808</v>
+        <v>1.784249242032042</v>
       </c>
       <c r="D108" t="n">
         <v>107</v>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-0.9542043501775823</v>
+        <v>1.785969343086812</v>
       </c>
       <c r="D109" t="n">
         <v>108</v>
@@ -2179,11 +2179,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-0.8886262767266497</v>
+        <v>1.795674660483478</v>
       </c>
       <c r="D110" t="n">
         <v>109</v>
@@ -2195,11 +2195,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-0.7591545561766914</v>
+        <v>1.797378385153318</v>
       </c>
       <c r="D111" t="n">
         <v>110</v>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.6935002249558597</v>
+        <v>1.79937784541014</v>
       </c>
       <c r="D112" t="n">
         <v>111</v>
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-0.6819864824319706</v>
+        <v>1.80810907507018</v>
       </c>
       <c r="D113" t="n">
         <v>112</v>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-0.6637302691957245</v>
+        <v>1.814455438241374</v>
       </c>
       <c r="D114" t="n">
         <v>113</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-0.6457202724962933</v>
+        <v>1.816743412061474</v>
       </c>
       <c r="D115" t="n">
         <v>114</v>
@@ -2275,11 +2275,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-0.6131065608954915</v>
+        <v>1.817001513462317</v>
       </c>
       <c r="D116" t="n">
         <v>115</v>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>DR-155</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-0.6115133564953452</v>
+        <v>1.82187143777675</v>
       </c>
       <c r="D117" t="n">
         <v>116</v>
@@ -2307,11 +2307,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>LSC-20</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-0.5688762431227989</v>
+        <v>1.828585017183645</v>
       </c>
       <c r="D118" t="n">
         <v>117</v>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-0.5123016982644781</v>
+        <v>1.832242825805457</v>
       </c>
       <c r="D119" t="n">
         <v>118</v>
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-0.4591346569471696</v>
+        <v>1.833284880776534</v>
       </c>
       <c r="D120" t="n">
         <v>119</v>
@@ -2355,11 +2355,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-0.4445858262261141</v>
+        <v>1.834147204615234</v>
       </c>
       <c r="D121" t="n">
         <v>120</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-0.4295471535086562</v>
+        <v>1.835532117225147</v>
       </c>
       <c r="D122" t="n">
         <v>121</v>
@@ -2387,11 +2387,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-0.4136621005620263</v>
+        <v>1.837347169913431</v>
       </c>
       <c r="D123" t="n">
         <v>122</v>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>DR-156</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-0.4095655588128816</v>
+        <v>1.840882362371848</v>
       </c>
       <c r="D124" t="n">
         <v>123</v>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-0.4032446095993193</v>
+        <v>1.842139772736655</v>
       </c>
       <c r="D125" t="n">
         <v>124</v>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-0.2374432786028324</v>
+        <v>1.844019583338982</v>
       </c>
       <c r="D126" t="n">
         <v>125</v>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-0.2265640866639765</v>
+        <v>1.849092762983925</v>
       </c>
       <c r="D127" t="n">
         <v>126</v>
@@ -2467,11 +2467,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-0.2213021407340587</v>
+        <v>1.849325257290956</v>
       </c>
       <c r="D128" t="n">
         <v>127</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-0.06628097554298429</v>
+        <v>1.851182818123461</v>
       </c>
       <c r="D129" t="n">
         <v>128</v>
@@ -2499,11 +2499,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-0.0504281816013018</v>
+        <v>1.852236771942578</v>
       </c>
       <c r="D130" t="n">
         <v>129</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.06820622532727638</v>
+        <v>1.852385601557556</v>
       </c>
       <c r="D131" t="n">
         <v>130</v>
@@ -2531,11 +2531,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.140095521734675</v>
+        <v>1.855526976173701</v>
       </c>
       <c r="D132" t="n">
         <v>131</v>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.172106207509748</v>
+        <v>1.858230150562333</v>
       </c>
       <c r="D133" t="n">
         <v>132</v>
@@ -2563,11 +2563,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.1892484853217944</v>
+        <v>1.863796454265291</v>
       </c>
       <c r="D134" t="n">
         <v>133</v>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.2886403532412899</v>
+        <v>1.868851751675448</v>
       </c>
       <c r="D135" t="n">
         <v>134</v>
@@ -2595,11 +2595,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>LSC-28</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.3371140007776494</v>
+        <v>1.871073894080778</v>
       </c>
       <c r="D136" t="n">
         <v>135</v>
@@ -2611,11 +2611,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>LSC-54</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.49324976933939</v>
+        <v>1.872734686993744</v>
       </c>
       <c r="D137" t="n">
         <v>136</v>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.5393268390483814</v>
+        <v>1.872941305291851</v>
       </c>
       <c r="D138" t="n">
         <v>137</v>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.5629463774175526</v>
+        <v>1.873533167999287</v>
       </c>
       <c r="D139" t="n">
         <v>138</v>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>LSC-33</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.5659713721060877</v>
+        <v>1.876535264191523</v>
       </c>
       <c r="D140" t="n">
         <v>139</v>
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.5809868471088423</v>
+        <v>1.87941412479793</v>
       </c>
       <c r="D141" t="n">
         <v>140</v>
@@ -2691,11 +2691,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.6180088988186799</v>
+        <v>1.883665089635062</v>
       </c>
       <c r="D142" t="n">
         <v>141</v>
@@ -2707,11 +2707,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.7004643741638442</v>
+        <v>1.887646008062042</v>
       </c>
       <c r="D143" t="n">
         <v>142</v>
@@ -2723,11 +2723,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.7308312681376758</v>
+        <v>1.88767175753047</v>
       </c>
       <c r="D144" t="n">
         <v>143</v>
@@ -2739,11 +2739,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.7670161598215928</v>
+        <v>1.88858662279881</v>
       </c>
       <c r="D145" t="n">
         <v>144</v>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>LSC-46</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.8233755248822641</v>
+        <v>1.890079953544512</v>
       </c>
       <c r="D146" t="n">
         <v>145</v>
@@ -2771,11 +2771,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>LSC-51</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.9958979042348548</v>
+        <v>1.891174593147191</v>
       </c>
       <c r="D147" t="n">
         <v>146</v>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>LSC-61</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1.023517559990041</v>
+        <v>1.892388237131291</v>
       </c>
       <c r="D148" t="n">
         <v>147</v>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1.084806202959793</v>
+        <v>1.895573090369167</v>
       </c>
       <c r="D149" t="n">
         <v>148</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1.202636293057992</v>
+        <v>1.896514514304374</v>
       </c>
       <c r="D150" t="n">
         <v>149</v>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1.240720923818688</v>
+        <v>1.903293889024335</v>
       </c>
       <c r="D151" t="n">
         <v>150</v>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1.244740382922031</v>
+        <v>1.905004309906836</v>
       </c>
       <c r="D152" t="n">
         <v>151</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1.306343721320207</v>
+        <v>1.908125374353101</v>
       </c>
       <c r="D153" t="n">
         <v>152</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>LSC-31</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1.328586088250863</v>
+        <v>1.908819522785173</v>
       </c>
       <c r="D154" t="n">
         <v>153</v>
@@ -2899,11 +2899,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1.422984192406221</v>
+        <v>1.909949433408192</v>
       </c>
       <c r="D155" t="n">
         <v>154</v>
@@ -2915,11 +2915,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>LSC-44</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1.436691716346055</v>
+        <v>1.912531287686928</v>
       </c>
       <c r="D156" t="n">
         <v>155</v>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1.441563767440232</v>
+        <v>1.920381692727967</v>
       </c>
       <c r="D157" t="n">
         <v>156</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>LSC-36</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1.455724127258949</v>
+        <v>1.92151550971351</v>
       </c>
       <c r="D158" t="n">
         <v>157</v>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1.528777531273058</v>
+        <v>1.922146077611095</v>
       </c>
       <c r="D159" t="n">
         <v>158</v>
@@ -2979,11 +2979,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-35</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1.561899450826634</v>
+        <v>1.927805850353364</v>
       </c>
       <c r="D160" t="n">
         <v>159</v>
@@ -2995,11 +2995,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1.782955583519249</v>
+        <v>1.931182220810229</v>
       </c>
       <c r="D161" t="n">
         <v>160</v>
@@ -3011,11 +3011,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1.789251504757831</v>
+        <v>1.936628783695056</v>
       </c>
       <c r="D162" t="n">
         <v>161</v>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>LSC-29</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1.79261628926828</v>
+        <v>1.949036716522095</v>
       </c>
       <c r="D163" t="n">
         <v>162</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1.826986330455241</v>
+        <v>1.949250100559077</v>
       </c>
       <c r="D164" t="n">
         <v>163</v>
@@ -3059,11 +3059,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1.890732861937404</v>
+        <v>1.958028088642536</v>
       </c>
       <c r="D165" t="n">
         <v>164</v>
@@ -3075,11 +3075,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1.91479598779764</v>
+        <v>1.958061368422979</v>
       </c>
       <c r="D166" t="n">
         <v>165</v>
@@ -3091,11 +3091,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.988942573301032</v>
+        <v>1.960217212494253</v>
       </c>
       <c r="D167" t="n">
         <v>166</v>
@@ -3107,11 +3107,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-150</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2.000314396412177</v>
+        <v>1.961100139535936</v>
       </c>
       <c r="D168" t="n">
         <v>167</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>LSC-63</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2.062392479299338</v>
+        <v>1.970285004112957</v>
       </c>
       <c r="D169" t="n">
         <v>168</v>
@@ -3139,11 +3139,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2.068315213778967</v>
+        <v>1.97135490205765</v>
       </c>
       <c r="D170" t="n">
         <v>169</v>
@@ -3155,11 +3155,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2.179102466421639</v>
+        <v>1.972685544435256</v>
       </c>
       <c r="D171" t="n">
         <v>170</v>
@@ -3171,11 +3171,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2.22878959637643</v>
+        <v>1.985566980443301</v>
       </c>
       <c r="D172" t="n">
         <v>171</v>
@@ -3187,11 +3187,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2.296253374541168</v>
+        <v>1.988188202597167</v>
       </c>
       <c r="D173" t="n">
         <v>172</v>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2.310301702762307</v>
+        <v>1.98835269915855</v>
       </c>
       <c r="D174" t="n">
         <v>173</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2.317656374873265</v>
+        <v>1.991468276109557</v>
       </c>
       <c r="D175" t="n">
         <v>174</v>
@@ -3235,11 +3235,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>LSC-49</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2.368692299963941</v>
+        <v>1.991793427020284</v>
       </c>
       <c r="D176" t="n">
         <v>175</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>LSC-34</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2.380171178330807</v>
+        <v>2.000020254490489</v>
       </c>
       <c r="D177" t="n">
         <v>176</v>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2.443868694700753</v>
+        <v>2.005413764590164</v>
       </c>
       <c r="D178" t="n">
         <v>177</v>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>LSC-52</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2.602352805827155</v>
+        <v>2.008144098733449</v>
       </c>
       <c r="D179" t="n">
         <v>178</v>
@@ -3299,11 +3299,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>LSC-50</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2.632185626256154</v>
+        <v>2.008884083501608</v>
       </c>
       <c r="D180" t="n">
         <v>179</v>
@@ -3315,11 +3315,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2.713722659289608</v>
+        <v>2.012404601209326</v>
       </c>
       <c r="D181" t="n">
         <v>180</v>
@@ -3331,11 +3331,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2.724284957849016</v>
+        <v>2.016710458497286</v>
       </c>
       <c r="D182" t="n">
         <v>181</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2.819258408382049</v>
+        <v>2.018117268740813</v>
       </c>
       <c r="D183" t="n">
         <v>182</v>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3.027344015601057</v>
+        <v>2.018398240087811</v>
       </c>
       <c r="D184" t="n">
         <v>183</v>
@@ -3379,11 +3379,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3.033690895756802</v>
+        <v>2.026218569728077</v>
       </c>
       <c r="D185" t="n">
         <v>184</v>
@@ -3395,11 +3395,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>SCR-05</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3.06241371478278</v>
+        <v>2.02785013471049</v>
       </c>
       <c r="D186" t="n">
         <v>185</v>
@@ -3411,11 +3411,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3.111529434587468</v>
+        <v>2.034685308983355</v>
       </c>
       <c r="D187" t="n">
         <v>186</v>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3.256061200682942</v>
+        <v>2.043188798254071</v>
       </c>
       <c r="D188" t="n">
         <v>187</v>
@@ -3443,11 +3443,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3.257064140483741</v>
+        <v>2.044164042330892</v>
       </c>
       <c r="D189" t="n">
         <v>188</v>
@@ -3459,11 +3459,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3.31807790391069</v>
+        <v>2.046722449898591</v>
       </c>
       <c r="D190" t="n">
         <v>189</v>
@@ -3475,11 +3475,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3.365369660364951</v>
+        <v>2.049431313331318</v>
       </c>
       <c r="D191" t="n">
         <v>190</v>
@@ -3491,11 +3491,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3.680379185734977</v>
+        <v>2.064521789994401</v>
       </c>
       <c r="D192" t="n">
         <v>191</v>
@@ -3507,11 +3507,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3.771129961104986</v>
+        <v>2.065130085085554</v>
       </c>
       <c r="D193" t="n">
         <v>192</v>
@@ -3523,11 +3523,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>DR-149</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3.779758408874764</v>
+        <v>2.072953875779553</v>
       </c>
       <c r="D194" t="n">
         <v>193</v>
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3.790973384713912</v>
+        <v>2.081002824992755</v>
       </c>
       <c r="D195" t="n">
         <v>194</v>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3.797260880298193</v>
+        <v>2.081316375321893</v>
       </c>
       <c r="D196" t="n">
         <v>195</v>
@@ -3571,11 +3571,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3.797628319046731</v>
+        <v>2.083250363831275</v>
       </c>
       <c r="D197" t="n">
         <v>196</v>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3.835545877538793</v>
+        <v>2.084039893130901</v>
       </c>
       <c r="D198" t="n">
         <v>197</v>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-154</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>3.837458472037349</v>
+        <v>2.085891368262413</v>
       </c>
       <c r="D199" t="n">
         <v>198</v>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>4.095082947534874</v>
+        <v>2.086703795324099</v>
       </c>
       <c r="D200" t="n">
         <v>199</v>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4.102580822655615</v>
+        <v>2.088040329544943</v>
       </c>
       <c r="D201" t="n">
         <v>200</v>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4.128308785060249</v>
+        <v>2.088949971589709</v>
       </c>
       <c r="D202" t="n">
         <v>201</v>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-158</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>4.339156322456247</v>
+        <v>2.090306596250556</v>
       </c>
       <c r="D203" t="n">
         <v>202</v>
@@ -3683,11 +3683,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>SCR-07</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>4.359363378431035</v>
+        <v>2.091113044120294</v>
       </c>
       <c r="D204" t="n">
         <v>203</v>
@@ -3699,11 +3699,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-147</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>4.522305970849448</v>
+        <v>2.094223202697414</v>
       </c>
       <c r="D205" t="n">
         <v>204</v>
@@ -3715,11 +3715,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>4.582455343000344</v>
+        <v>2.096483224717089</v>
       </c>
       <c r="D206" t="n">
         <v>205</v>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>4.70792757008001</v>
+        <v>2.10535634101537</v>
       </c>
       <c r="D207" t="n">
         <v>206</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4.743431511603315</v>
+        <v>2.116230317482735</v>
       </c>
       <c r="D208" t="n">
         <v>207</v>
@@ -3763,11 +3763,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>5.069724879076849</v>
+        <v>2.11669539454337</v>
       </c>
       <c r="D209" t="n">
         <v>208</v>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>DR-146</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>5.219261352581796</v>
+        <v>2.120532249548834</v>
       </c>
       <c r="D210" t="n">
         <v>209</v>
@@ -3795,11 +3795,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>5.287726803825795</v>
+        <v>2.125722414965174</v>
       </c>
       <c r="D211" t="n">
         <v>210</v>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>5.410417555488351</v>
+        <v>2.126749994648585</v>
       </c>
       <c r="D212" t="n">
         <v>211</v>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>5.45440648523253</v>
+        <v>2.127284864671742</v>
       </c>
       <c r="D213" t="n">
         <v>212</v>
@@ -3843,11 +3843,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>LSC-65</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>5.480026990128871</v>
+        <v>2.130772912792541</v>
       </c>
       <c r="D214" t="n">
         <v>213</v>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>5.528731378728785</v>
+        <v>2.135546246102705</v>
       </c>
       <c r="D215" t="n">
         <v>214</v>
@@ -3875,11 +3875,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>5.616666174333869</v>
+        <v>2.141542948187715</v>
       </c>
       <c r="D216" t="n">
         <v>215</v>
@@ -3891,11 +3891,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>5.639862559627898</v>
+        <v>2.148632970839489</v>
       </c>
       <c r="D217" t="n">
         <v>216</v>
@@ -3907,11 +3907,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>5.903358574383061</v>
+        <v>2.166148922456403</v>
       </c>
       <c r="D218" t="n">
         <v>217</v>
@@ -3923,11 +3923,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>LSC-64</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>5.995475629364829</v>
+        <v>2.172607852869704</v>
       </c>
       <c r="D219" t="n">
         <v>218</v>
@@ -3939,11 +3939,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>6.061938958827319</v>
+        <v>2.176647093965513</v>
       </c>
       <c r="D220" t="n">
         <v>219</v>
@@ -3955,11 +3955,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>6.498998653210989</v>
+        <v>2.17750024338224</v>
       </c>
       <c r="D221" t="n">
         <v>220</v>
@@ -3971,11 +3971,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>6.877894116815751</v>
+        <v>2.178932884511713</v>
       </c>
       <c r="D222" t="n">
         <v>221</v>
@@ -3987,11 +3987,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>6.904748360547603</v>
+        <v>2.190345473003363</v>
       </c>
       <c r="D223" t="n">
         <v>222</v>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>7.014331604878336</v>
+        <v>2.19143493912578</v>
       </c>
       <c r="D224" t="n">
         <v>223</v>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>7.092194982282656</v>
+        <v>2.203451569486536</v>
       </c>
       <c r="D225" t="n">
         <v>224</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>7.255717804581041</v>
+        <v>2.203822381661385</v>
       </c>
       <c r="D226" t="n">
         <v>225</v>
@@ -4051,11 +4051,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>7.296760852853477</v>
+        <v>2.204136658833137</v>
       </c>
       <c r="D227" t="n">
         <v>226</v>
@@ -4067,11 +4067,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>7.379207310869586</v>
+        <v>2.204176982354598</v>
       </c>
       <c r="D228" t="n">
         <v>227</v>
@@ -4083,11 +4083,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>7.546725419494346</v>
+        <v>2.205737550664038</v>
       </c>
       <c r="D229" t="n">
         <v>228</v>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>7.692681901639905</v>
+        <v>2.206882229904289</v>
       </c>
       <c r="D230" t="n">
         <v>229</v>
@@ -4115,11 +4115,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>7.956443995041351</v>
+        <v>2.216955541102134</v>
       </c>
       <c r="D231" t="n">
         <v>230</v>
@@ -4131,11 +4131,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>8.355052443775538</v>
+        <v>2.223881941993485</v>
       </c>
       <c r="D232" t="n">
         <v>231</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>9.758422029443398</v>
+        <v>2.223896127127902</v>
       </c>
       <c r="D233" t="n">
         <v>232</v>
@@ -4163,14 +4163,1246 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>10.50503389945685</v>
+        <v>2.225614607342026</v>
       </c>
       <c r="D234" t="n">
         <v>233</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>LSC-66</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2.225831461264398</v>
+      </c>
+      <c r="D235" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DR-113</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2.234670069502203</v>
+      </c>
+      <c r="D236" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DR-228</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2.237827733145832</v>
+      </c>
+      <c r="D237" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DR-100</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2.240698464588561</v>
+      </c>
+      <c r="D238" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>DR-96</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2.254554424530056</v>
+      </c>
+      <c r="D239" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DR-58</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2.255412267271748</v>
+      </c>
+      <c r="D240" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DR-104</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2.255460955039642</v>
+      </c>
+      <c r="D241" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2.256684013059453</v>
+      </c>
+      <c r="D242" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DR-214</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2.257114407720129</v>
+      </c>
+      <c r="D243" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>DR-07</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2.259617052322659</v>
+      </c>
+      <c r="D244" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DR-107</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2.259665662626821</v>
+      </c>
+      <c r="D245" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>LSC-13</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2.266317888729191</v>
+      </c>
+      <c r="D246" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DR-97</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2.274104618603809</v>
+      </c>
+      <c r="D247" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DR-62</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2.282875574279874</v>
+      </c>
+      <c r="D248" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>DR-229</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2.284128560208866</v>
+      </c>
+      <c r="D249" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>DR-220</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2.292223632375156</v>
+      </c>
+      <c r="D250" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>DR-34</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2.292972393683529</v>
+      </c>
+      <c r="D251" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>DR-61</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2.296875612013175</v>
+      </c>
+      <c r="D252" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>DR-93</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2.297143345271413</v>
+      </c>
+      <c r="D253" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DR-105</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2.30436021976333</v>
+      </c>
+      <c r="D254" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>DR-63</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2.30486265002722</v>
+      </c>
+      <c r="D255" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>DR-180</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2.3080956171541</v>
+      </c>
+      <c r="D256" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>DR-13</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2.313208908872125</v>
+      </c>
+      <c r="D257" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>DR-212</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2.314180477869079</v>
+      </c>
+      <c r="D258" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>DR-91</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2.316945052472657</v>
+      </c>
+      <c r="D259" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>DR-77</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2.318957803555949</v>
+      </c>
+      <c r="D260" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>DR-221</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>2.330870386706418</v>
+      </c>
+      <c r="D261" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>DR-90</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2.335668552758849</v>
+      </c>
+      <c r="D262" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DR-219</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2.346199314269018</v>
+      </c>
+      <c r="D263" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>DR-101</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2.348258009303215</v>
+      </c>
+      <c r="D264" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>DR-82</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2.348721230239666</v>
+      </c>
+      <c r="D265" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>DR-89</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>2.351987073613496</v>
+      </c>
+      <c r="D266" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>DR-67</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>2.358760136520586</v>
+      </c>
+      <c r="D267" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>DR-102</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>2.359783330369048</v>
+      </c>
+      <c r="D268" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>DR-69</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>2.36314673404761</v>
+      </c>
+      <c r="D269" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>DR-116</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2.36703624029589</v>
+      </c>
+      <c r="D270" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>2.368060561585506</v>
+      </c>
+      <c r="D271" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>DR-68</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2.372058461372703</v>
+      </c>
+      <c r="D272" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>DR-75</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2.374953150857532</v>
+      </c>
+      <c r="D273" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>DR-99</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2.376235026414684</v>
+      </c>
+      <c r="D274" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>DR-135</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>2.38494398826685</v>
+      </c>
+      <c r="D275" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>DR-02</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2.39194196653103</v>
+      </c>
+      <c r="D276" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>DR-161</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2.393590691441895</v>
+      </c>
+      <c r="D277" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>DR-117</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2.396016929997975</v>
+      </c>
+      <c r="D278" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>DR-66</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2.397511512949263</v>
+      </c>
+      <c r="D279" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>DR-124</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>2.401502497806764</v>
+      </c>
+      <c r="D280" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>DR-78</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>2.405839589865746</v>
+      </c>
+      <c r="D281" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>DR-134</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2.4168979905181</v>
+      </c>
+      <c r="D282" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>DR-122</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2.422787695365836</v>
+      </c>
+      <c r="D283" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>DR-213</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>2.426771971913964</v>
+      </c>
+      <c r="D284" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>DR-211</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2.428814020697357</v>
+      </c>
+      <c r="D285" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>DR-114</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>2.4423036152023</v>
+      </c>
+      <c r="D286" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>DR-224</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>2.452432568727802</v>
+      </c>
+      <c r="D287" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>DR-72</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>2.453079648755606</v>
+      </c>
+      <c r="D288" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>DR-92</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>2.453571057280282</v>
+      </c>
+      <c r="D289" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>DR-210</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>2.454169640740191</v>
+      </c>
+      <c r="D290" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>DR-187</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2.457863055672472</v>
+      </c>
+      <c r="D291" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>DR-190</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2.470978398980838</v>
+      </c>
+      <c r="D292" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>DR-217</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2.480516179683955</v>
+      </c>
+      <c r="D293" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>DR-79</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2.490232968012455</v>
+      </c>
+      <c r="D294" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>DR-106</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>2.492312144090535</v>
+      </c>
+      <c r="D295" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>DR-234</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>2.519171985976699</v>
+      </c>
+      <c r="D296" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>DR-120</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>2.524351354525623</v>
+      </c>
+      <c r="D297" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>DR-218</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>2.529428290251174</v>
+      </c>
+      <c r="D298" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>297</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>DR-115</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>2.547750144832546</v>
+      </c>
+      <c r="D299" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>298</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>DR-118</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>2.579469130443514</v>
+      </c>
+      <c r="D300" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>DR-60</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2.584000025092682</v>
+      </c>
+      <c r="D301" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>DR-06</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>2.605927234642048</v>
+      </c>
+      <c r="D302" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>DR-119</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2.62024303491666</v>
+      </c>
+      <c r="D303" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>302</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>DR-73</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2.621194705301892</v>
+      </c>
+      <c r="D304" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>303</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>DR-81</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2.624215029366092</v>
+      </c>
+      <c r="D305" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>DR-84</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2.640653492217719</v>
+      </c>
+      <c r="D306" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>DR-111</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>2.703076605509886</v>
+      </c>
+      <c r="D307" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>306</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>DR-70</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>2.7795796897841</v>
+      </c>
+      <c r="D308" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>307</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>DR-64</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2.787062342419811</v>
+      </c>
+      <c r="D309" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>DR-80</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>2.8140454359108</v>
+      </c>
+      <c r="D310" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>309</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>DR-138</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>2.922053110669861</v>
+      </c>
+      <c r="D311" t="n">
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/PCA_Stressors/tables/SumRel_site_rankings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/SumRel_site_rankings.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8757009819408152</v>
+        <v>0.7056207681741683</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,11 +467,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9894938356146357</v>
+        <v>0.7535426729930967</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.121643085678034</v>
+        <v>0.8072269551664539</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.14091151471174</v>
+        <v>0.8580699266856244</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -515,11 +515,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.178571299416075</v>
+        <v>0.8998707742494801</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -531,11 +531,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.188744169565138</v>
+        <v>0.9607782257285012</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -547,11 +547,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.197514984370817</v>
+        <v>0.9679782338556194</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -563,11 +563,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.203952743873251</v>
+        <v>0.9871682130823791</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -579,11 +579,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.211641528286106</v>
+        <v>1.000147698940994</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -595,11 +595,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.241038451205754</v>
+        <v>1.022254368713305</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -611,11 +611,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.257063412161886</v>
+        <v>1.029025632334613</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -627,11 +627,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.292101778402669</v>
+        <v>1.060464007588855</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -643,11 +643,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.313871199859042</v>
+        <v>1.094525944212324</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -659,11 +659,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.328582602333761</v>
+        <v>1.099753733846578</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.353105389684064</v>
+        <v>1.112521982847365</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.362206860533212</v>
+        <v>1.12287057848717</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -707,11 +707,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.366378450025826</v>
+        <v>1.131009489862712</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -723,11 +723,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.390860702083689</v>
+        <v>1.150904693159955</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -739,11 +739,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.393934924195571</v>
+        <v>1.156046629372816</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -755,11 +755,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.398359703675624</v>
+        <v>1.189992537660774</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -771,11 +771,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.417547588632952</v>
+        <v>1.199793028748418</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -787,11 +787,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.424180086333783</v>
+        <v>1.206277957693201</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -803,11 +803,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.440067743901287</v>
+        <v>1.216665444317556</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
@@ -819,11 +819,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.442066646114398</v>
+        <v>1.224198032237091</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -835,11 +835,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.451848181104439</v>
+        <v>1.230534165465965</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
@@ -851,11 +851,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.467481933616187</v>
+        <v>1.249365148255584</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
@@ -867,11 +867,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DR-157</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.478471109682633</v>
+        <v>1.281231746398265</v>
       </c>
       <c r="D28" t="n">
         <v>27</v>
@@ -883,11 +883,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.486661628571753</v>
+        <v>1.289959495185142</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
@@ -899,11 +899,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.486668689272614</v>
+        <v>1.302351939453433</v>
       </c>
       <c r="D30" t="n">
         <v>29</v>
@@ -915,11 +915,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.495126099100238</v>
+        <v>1.310941176823576</v>
       </c>
       <c r="D31" t="n">
         <v>30</v>
@@ -931,11 +931,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.49812549377652</v>
+        <v>1.320762342834007</v>
       </c>
       <c r="D32" t="n">
         <v>31</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.500963200559916</v>
+        <v>1.332662049561272</v>
       </c>
       <c r="D33" t="n">
         <v>32</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.503430985927214</v>
+        <v>1.341960007959302</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -979,11 +979,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.503540936109761</v>
+        <v>1.359802282139845</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.505515821228682</v>
+        <v>1.37683176909306</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.508165646919392</v>
+        <v>1.38137360235791</v>
       </c>
       <c r="D37" t="n">
         <v>36</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.518525973087024</v>
+        <v>1.383779218588081</v>
       </c>
       <c r="D38" t="n">
         <v>37</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.518811354151904</v>
+        <v>1.385593062162153</v>
       </c>
       <c r="D39" t="n">
         <v>38</v>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.520808695996315</v>
+        <v>1.387350322343518</v>
       </c>
       <c r="D40" t="n">
         <v>39</v>
@@ -1075,11 +1075,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DR-03</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.524349086095014</v>
+        <v>1.394163300492952</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.528140502565595</v>
+        <v>1.397096812605659</v>
       </c>
       <c r="D42" t="n">
         <v>41</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.53368466317342</v>
+        <v>1.403613032383594</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.569334203393288</v>
+        <v>1.405384057255075</v>
       </c>
       <c r="D44" t="n">
         <v>43</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.570481963046426</v>
+        <v>1.408377007933915</v>
       </c>
       <c r="D45" t="n">
         <v>44</v>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.57142651631452</v>
+        <v>1.414363251887464</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DR-22</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.573282739034406</v>
+        <v>1.417536211870674</v>
       </c>
       <c r="D47" t="n">
         <v>46</v>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DR-24</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.575922144773402</v>
+        <v>1.421738839022065</v>
       </c>
       <c r="D48" t="n">
         <v>47</v>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DR-191</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.579754808826731</v>
+        <v>1.438492804810042</v>
       </c>
       <c r="D49" t="n">
         <v>48</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.581937322093751</v>
+        <v>1.438586442263281</v>
       </c>
       <c r="D50" t="n">
         <v>49</v>
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DR-193</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.585509022662273</v>
+        <v>1.448346927202338</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DR-159</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.590503873146879</v>
+        <v>1.451963873961001</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
@@ -1267,11 +1267,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.590615617364291</v>
+        <v>1.454003138179674</v>
       </c>
       <c r="D53" t="n">
         <v>52</v>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DR-169</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.592123527375639</v>
+        <v>1.455436759629273</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DR-29</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.592457738419646</v>
+        <v>1.464797275996105</v>
       </c>
       <c r="D55" t="n">
         <v>54</v>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.592805311151601</v>
+        <v>1.471129058954918</v>
       </c>
       <c r="D56" t="n">
         <v>55</v>
@@ -1331,11 +1331,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DR-12</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.59590103954848</v>
+        <v>1.474543311617011</v>
       </c>
       <c r="D57" t="n">
         <v>56</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SCR-10</t>
+          <t>DR-156</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.602339029925951</v>
+        <v>1.478795924639386</v>
       </c>
       <c r="D58" t="n">
         <v>57</v>
@@ -1363,11 +1363,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DR-148</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.603465383395154</v>
+        <v>1.478954114701149</v>
       </c>
       <c r="D59" t="n">
         <v>58</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DR-30</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.611302977050177</v>
+        <v>1.486144414507158</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DR-28</t>
+          <t>LSC-31</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.615587549238018</v>
+        <v>1.497428231964446</v>
       </c>
       <c r="D61" t="n">
         <v>60</v>
@@ -1411,11 +1411,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DR-16</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.615607344736268</v>
+        <v>1.503009685497868</v>
       </c>
       <c r="D62" t="n">
         <v>61</v>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LSC-12</t>
+          <t>LSC-28</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.623760967257978</v>
+        <v>1.528124967451991</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.626778857386204</v>
+        <v>1.539858585066535</v>
       </c>
       <c r="D64" t="n">
         <v>63</v>
@@ -1459,11 +1459,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DR-184</t>
+          <t>LSC-46</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.62830561492514</v>
+        <v>1.54752311681832</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-35</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.635113606183217</v>
+        <v>1.548263866958858</v>
       </c>
       <c r="D66" t="n">
         <v>65</v>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DR-52</t>
+          <t>LSC-29</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.639617844905057</v>
+        <v>1.552959399873862</v>
       </c>
       <c r="D67" t="n">
         <v>66</v>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.642962111862984</v>
+        <v>1.563015267106128</v>
       </c>
       <c r="D68" t="n">
         <v>67</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DR-98</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.648942604025713</v>
+        <v>1.564855968073542</v>
       </c>
       <c r="D69" t="n">
         <v>68</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.657598486022446</v>
+        <v>1.582722220996061</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.661334682760783</v>
+        <v>1.585472152906322</v>
       </c>
       <c r="D71" t="n">
         <v>70</v>
@@ -1571,11 +1571,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DR-198</t>
+          <t>LSC-44</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.662046313159057</v>
+        <v>1.601326332089036</v>
       </c>
       <c r="D72" t="n">
         <v>71</v>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DR-153</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.666514154770887</v>
+        <v>1.608649258657675</v>
       </c>
       <c r="D73" t="n">
         <v>72</v>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.66779747306475</v>
+        <v>1.608966831888634</v>
       </c>
       <c r="D74" t="n">
         <v>73</v>
@@ -1619,11 +1619,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.668352233211897</v>
+        <v>1.61118195683036</v>
       </c>
       <c r="D75" t="n">
         <v>74</v>
@@ -1635,11 +1635,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DR-25</t>
+          <t>LSC-51</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.670382642350369</v>
+        <v>1.613936498729886</v>
       </c>
       <c r="D76" t="n">
         <v>75</v>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.6711609754695</v>
+        <v>1.614084413093006</v>
       </c>
       <c r="D77" t="n">
         <v>76</v>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.674647114460876</v>
+        <v>1.621562537633545</v>
       </c>
       <c r="D78" t="n">
         <v>77</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DR-194</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.674982653951614</v>
+        <v>1.627338738781431</v>
       </c>
       <c r="D79" t="n">
         <v>78</v>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.678923181244775</v>
+        <v>1.633984681417352</v>
       </c>
       <c r="D80" t="n">
         <v>79</v>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DR-57</t>
+          <t>LSC-33</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.680035042257388</v>
+        <v>1.641805523310704</v>
       </c>
       <c r="D81" t="n">
         <v>80</v>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DR-152</t>
+          <t>LSC-54</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.681065236127189</v>
+        <v>1.651727266056201</v>
       </c>
       <c r="D82" t="n">
         <v>81</v>
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DR-47</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.681199253639464</v>
+        <v>1.676671675635197</v>
       </c>
       <c r="D83" t="n">
         <v>82</v>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.684072709393042</v>
+        <v>1.686249568139959</v>
       </c>
       <c r="D84" t="n">
         <v>83</v>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DR-178</t>
+          <t>LSC-36</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.692057886931791</v>
+        <v>1.686250256306184</v>
       </c>
       <c r="D85" t="n">
         <v>84</v>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DR-199</t>
+          <t>DR-155</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.692311346145622</v>
+        <v>1.696562814142636</v>
       </c>
       <c r="D86" t="n">
         <v>85</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-20</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.703848510508728</v>
+        <v>1.697052012644586</v>
       </c>
       <c r="D87" t="n">
         <v>86</v>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.711075856795166</v>
+        <v>1.700032696910861</v>
       </c>
       <c r="D88" t="n">
         <v>87</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.71183269889984</v>
+        <v>1.708934830467151</v>
       </c>
       <c r="D89" t="n">
         <v>88</v>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.717817283583649</v>
+        <v>1.714398773161739</v>
       </c>
       <c r="D90" t="n">
         <v>89</v>
@@ -1875,11 +1875,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-52</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.71851742253445</v>
+        <v>1.721946046437417</v>
       </c>
       <c r="D91" t="n">
         <v>90</v>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.720956427424588</v>
+        <v>1.722131615491072</v>
       </c>
       <c r="D92" t="n">
         <v>91</v>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DR-42</t>
+          <t>LSC-63</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.727615666239964</v>
+        <v>1.732844831986558</v>
       </c>
       <c r="D93" t="n">
         <v>92</v>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DR-35</t>
+          <t>LSC-61</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.728831537770571</v>
+        <v>1.739262018800463</v>
       </c>
       <c r="D94" t="n">
         <v>93</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DR-196</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.731079539231763</v>
+        <v>1.741445497862685</v>
       </c>
       <c r="D95" t="n">
         <v>94</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DR-201</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.736811572256539</v>
+        <v>1.742341619394473</v>
       </c>
       <c r="D96" t="n">
         <v>95</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DR-226</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.738954699200735</v>
+        <v>1.748262846501743</v>
       </c>
       <c r="D97" t="n">
         <v>96</v>
@@ -1987,11 +1987,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DR-103</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.741515462795688</v>
+        <v>1.750547879689813</v>
       </c>
       <c r="D98" t="n">
         <v>97</v>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DR-203</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.749234351293034</v>
+        <v>1.752704882425619</v>
       </c>
       <c r="D99" t="n">
         <v>98</v>
@@ -2019,11 +2019,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.756042382798823</v>
+        <v>1.755970020800611</v>
       </c>
       <c r="D100" t="n">
         <v>99</v>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.761085045435297</v>
+        <v>1.759222433998556</v>
       </c>
       <c r="D101" t="n">
         <v>100</v>
@@ -2051,11 +2051,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DR-235</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.764420820455963</v>
+        <v>1.777172725370856</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2067,11 +2067,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DR-225</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.766646081349474</v>
+        <v>1.785140573888917</v>
       </c>
       <c r="D103" t="n">
         <v>102</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LSC-07</t>
+          <t>LSC-34</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.776910899095918</v>
+        <v>1.789679763313964</v>
       </c>
       <c r="D104" t="n">
         <v>103</v>
@@ -2099,11 +2099,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DR-08</t>
+          <t>LSC-50</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.777415381980655</v>
+        <v>1.793090484301416</v>
       </c>
       <c r="D105" t="n">
         <v>104</v>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1.782061461074954</v>
+        <v>1.798532866100305</v>
       </c>
       <c r="D106" t="n">
         <v>105</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SCR-13</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.783649164944135</v>
+        <v>1.808636973613482</v>
       </c>
       <c r="D107" t="n">
         <v>106</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DR-151</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1.784249242032042</v>
+        <v>1.811115000018269</v>
       </c>
       <c r="D108" t="n">
         <v>107</v>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>DR-152</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.785969343086812</v>
+        <v>1.819977381567117</v>
       </c>
       <c r="D109" t="n">
         <v>108</v>
@@ -2179,11 +2179,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DR-232</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.795674660483478</v>
+        <v>1.82623644168129</v>
       </c>
       <c r="D110" t="n">
         <v>109</v>
@@ -2195,11 +2195,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DR-230</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.797378385153318</v>
+        <v>1.829461679936702</v>
       </c>
       <c r="D111" t="n">
         <v>110</v>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>LSC-49</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.79937784541014</v>
+        <v>1.831906388476222</v>
       </c>
       <c r="D112" t="n">
         <v>111</v>
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DR-189</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1.80810907507018</v>
+        <v>1.8332577283659</v>
       </c>
       <c r="D113" t="n">
         <v>112</v>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DR-09</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1.814455438241374</v>
+        <v>1.838728306647658</v>
       </c>
       <c r="D114" t="n">
         <v>113</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DR-142</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.816743412061474</v>
+        <v>1.841555183282661</v>
       </c>
       <c r="D115" t="n">
         <v>114</v>
@@ -2275,11 +2275,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1.817001513462317</v>
+        <v>1.851111205876621</v>
       </c>
       <c r="D116" t="n">
         <v>115</v>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DR-155</t>
+          <t>DR-149</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.82187143777675</v>
+        <v>1.866927510117839</v>
       </c>
       <c r="D117" t="n">
         <v>116</v>
@@ -2307,11 +2307,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LSC-20</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.828585017183645</v>
+        <v>1.873157885059524</v>
       </c>
       <c r="D118" t="n">
         <v>117</v>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DR-233</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.832242825805457</v>
+        <v>1.88067676033657</v>
       </c>
       <c r="D119" t="n">
         <v>118</v>
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1.833284880776534</v>
+        <v>1.883831030498765</v>
       </c>
       <c r="D120" t="n">
         <v>119</v>
@@ -2355,11 +2355,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DR-176</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.834147204615234</v>
+        <v>1.885445516605141</v>
       </c>
       <c r="D121" t="n">
         <v>120</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1.835532117225147</v>
+        <v>1.888979938339523</v>
       </c>
       <c r="D122" t="n">
         <v>121</v>
@@ -2387,11 +2387,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DR-182</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1.837347169913431</v>
+        <v>1.88970358323495</v>
       </c>
       <c r="D123" t="n">
         <v>122</v>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DR-156</t>
+          <t>DR-146</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.840882362371848</v>
+        <v>1.89136486379361</v>
       </c>
       <c r="D124" t="n">
         <v>123</v>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SCR-01</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1.842139772736655</v>
+        <v>1.897489696345346</v>
       </c>
       <c r="D125" t="n">
         <v>124</v>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>SCR-07</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1.844019583338982</v>
+        <v>1.900175548025983</v>
       </c>
       <c r="D126" t="n">
         <v>125</v>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DR-231</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.849092762983925</v>
+        <v>1.913882535998902</v>
       </c>
       <c r="D127" t="n">
         <v>126</v>
@@ -2467,11 +2467,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1.849325257290956</v>
+        <v>1.93204993501798</v>
       </c>
       <c r="D128" t="n">
         <v>127</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-05</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.851182818123461</v>
+        <v>1.932115237749426</v>
       </c>
       <c r="D129" t="n">
         <v>128</v>
@@ -2499,11 +2499,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SCR-12</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.852236771942578</v>
+        <v>1.936901480973675</v>
       </c>
       <c r="D130" t="n">
         <v>129</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DR-26</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1.852385601557556</v>
+        <v>1.939501989748543</v>
       </c>
       <c r="D131" t="n">
         <v>130</v>
@@ -2531,11 +2531,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DR-200</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1.855526976173701</v>
+        <v>1.941276662364709</v>
       </c>
       <c r="D132" t="n">
         <v>131</v>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DR-160</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1.858230150562333</v>
+        <v>1.942439065253653</v>
       </c>
       <c r="D133" t="n">
         <v>132</v>
@@ -2563,11 +2563,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1.863796454265291</v>
+        <v>1.948046309417244</v>
       </c>
       <c r="D134" t="n">
         <v>133</v>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.868851751675448</v>
+        <v>1.950264165375097</v>
       </c>
       <c r="D135" t="n">
         <v>134</v>
@@ -2595,11 +2595,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LSC-28</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1.871073894080778</v>
+        <v>1.982913658953167</v>
       </c>
       <c r="D136" t="n">
         <v>135</v>
@@ -2611,11 +2611,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LSC-54</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1.872734686993744</v>
+        <v>1.982933870251699</v>
       </c>
       <c r="D137" t="n">
         <v>136</v>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DR-11</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1.872941305291851</v>
+        <v>1.982997573166394</v>
       </c>
       <c r="D138" t="n">
         <v>137</v>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1.873533167999287</v>
+        <v>1.985639593199056</v>
       </c>
       <c r="D139" t="n">
         <v>138</v>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LSC-33</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1.876535264191523</v>
+        <v>1.99918540308028</v>
       </c>
       <c r="D140" t="n">
         <v>139</v>
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1.87941412479793</v>
+        <v>2.007057722047044</v>
       </c>
       <c r="D141" t="n">
         <v>140</v>
@@ -2691,11 +2691,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LSC-01</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1.883665089635062</v>
+        <v>2.012409173095774</v>
       </c>
       <c r="D142" t="n">
         <v>141</v>
@@ -2707,11 +2707,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DR-37</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1.887646008062042</v>
+        <v>2.013866523392402</v>
       </c>
       <c r="D143" t="n">
         <v>142</v>
@@ -2723,11 +2723,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DR-222</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1.88767175753047</v>
+        <v>2.018046248798753</v>
       </c>
       <c r="D144" t="n">
         <v>143</v>
@@ -2739,11 +2739,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DR-94</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1.88858662279881</v>
+        <v>2.021895831442953</v>
       </c>
       <c r="D145" t="n">
         <v>144</v>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LSC-46</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1.890079953544512</v>
+        <v>2.026247894023458</v>
       </c>
       <c r="D146" t="n">
         <v>145</v>
@@ -2771,11 +2771,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LSC-51</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1.891174593147191</v>
+        <v>2.030609814975738</v>
       </c>
       <c r="D147" t="n">
         <v>146</v>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LSC-61</t>
+          <t>DR-151</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1.892388237131291</v>
+        <v>2.033367118477135</v>
       </c>
       <c r="D148" t="n">
         <v>147</v>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DR-43</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1.895573090369167</v>
+        <v>2.053874382561521</v>
       </c>
       <c r="D149" t="n">
         <v>148</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DR-65</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1.896514514304374</v>
+        <v>2.056672706007561</v>
       </c>
       <c r="D150" t="n">
         <v>149</v>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LSC-03</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1.903293889024335</v>
+        <v>2.078545130777753</v>
       </c>
       <c r="D151" t="n">
         <v>150</v>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1.905004309906836</v>
+        <v>2.078747011059704</v>
       </c>
       <c r="D152" t="n">
         <v>151</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DR-188</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1.908125374353101</v>
+        <v>2.083616108656337</v>
       </c>
       <c r="D153" t="n">
         <v>152</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LSC-31</t>
+          <t>LSC-66</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1.908819522785173</v>
+        <v>2.083858845052325</v>
       </c>
       <c r="D154" t="n">
         <v>153</v>
@@ -2899,11 +2899,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SCR-16</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1.909949433408192</v>
+        <v>2.086705526873085</v>
       </c>
       <c r="D155" t="n">
         <v>154</v>
@@ -2915,11 +2915,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LSC-44</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1.912531287686928</v>
+        <v>2.090556786999183</v>
       </c>
       <c r="D156" t="n">
         <v>155</v>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1.920381692727967</v>
+        <v>2.093272599501539</v>
       </c>
       <c r="D157" t="n">
         <v>156</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LSC-36</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1.92151550971351</v>
+        <v>2.095130287054531</v>
       </c>
       <c r="D158" t="n">
         <v>157</v>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DR-36</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1.922146077611095</v>
+        <v>2.102651902151504</v>
       </c>
       <c r="D159" t="n">
         <v>158</v>
@@ -2979,11 +2979,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LSC-35</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1.927805850353364</v>
+        <v>2.104081493015014</v>
       </c>
       <c r="D160" t="n">
         <v>159</v>
@@ -2995,11 +2995,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DR-27</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1.931182220810229</v>
+        <v>2.108257863925743</v>
       </c>
       <c r="D161" t="n">
         <v>160</v>
@@ -3011,11 +3011,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SCR-02</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1.936628783695056</v>
+        <v>2.110222170778733</v>
       </c>
       <c r="D162" t="n">
         <v>161</v>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LSC-29</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1.949036716522095</v>
+        <v>2.117612110688755</v>
       </c>
       <c r="D163" t="n">
         <v>162</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DR-41</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1.949250100559077</v>
+        <v>2.125105640226749</v>
       </c>
       <c r="D164" t="n">
         <v>163</v>
@@ -3059,11 +3059,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1.958028088642536</v>
+        <v>2.127292095811363</v>
       </c>
       <c r="D165" t="n">
         <v>164</v>
@@ -3075,11 +3075,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DR-170</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1.958061368422979</v>
+        <v>2.133875240515586</v>
       </c>
       <c r="D166" t="n">
         <v>165</v>
@@ -3091,11 +3091,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SCR-15</t>
+          <t>LSC-65</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.960217212494253</v>
+        <v>2.134033618727055</v>
       </c>
       <c r="D167" t="n">
         <v>166</v>
@@ -3107,11 +3107,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DR-150</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1.961100139535936</v>
+        <v>2.134692680699723</v>
       </c>
       <c r="D168" t="n">
         <v>167</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LSC-63</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1.970285004112957</v>
+        <v>2.135140174043853</v>
       </c>
       <c r="D169" t="n">
         <v>168</v>
@@ -3139,11 +3139,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SCR-04</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1.97135490205765</v>
+        <v>2.137541394826543</v>
       </c>
       <c r="D170" t="n">
         <v>169</v>
@@ -3155,11 +3155,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DR-85</t>
+          <t>DR-154</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1.972685544435256</v>
+        <v>2.137773583379683</v>
       </c>
       <c r="D171" t="n">
         <v>170</v>
@@ -3171,11 +3171,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LSC-02</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1.985566980443301</v>
+        <v>2.146503558450973</v>
       </c>
       <c r="D172" t="n">
         <v>171</v>
@@ -3187,11 +3187,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DR-186</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1.988188202597167</v>
+        <v>2.147708619524935</v>
       </c>
       <c r="D173" t="n">
         <v>172</v>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LSC-05</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1.98835269915855</v>
+        <v>2.148709972357618</v>
       </c>
       <c r="D174" t="n">
         <v>173</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DR-39</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1.991468276109557</v>
+        <v>2.165379429888142</v>
       </c>
       <c r="D175" t="n">
         <v>174</v>
@@ -3235,11 +3235,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LSC-49</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.991793427020284</v>
+        <v>2.165387365439588</v>
       </c>
       <c r="D176" t="n">
         <v>175</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LSC-34</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2.000020254490489</v>
+        <v>2.170179368573807</v>
       </c>
       <c r="D177" t="n">
         <v>176</v>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DR-227</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2.005413764590164</v>
+        <v>2.177424616411376</v>
       </c>
       <c r="D178" t="n">
         <v>177</v>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LSC-52</t>
+          <t>DR-148</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2.008144098733449</v>
+        <v>2.194828847361144</v>
       </c>
       <c r="D179" t="n">
         <v>178</v>
@@ -3299,11 +3299,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LSC-50</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2.008884083501608</v>
+        <v>2.200420235805477</v>
       </c>
       <c r="D180" t="n">
         <v>179</v>
@@ -3315,11 +3315,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DR-04</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2.012404601209326</v>
+        <v>2.205332776842546</v>
       </c>
       <c r="D181" t="n">
         <v>180</v>
@@ -3331,11 +3331,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DR-110</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2.016710458497286</v>
+        <v>2.210896242498562</v>
       </c>
       <c r="D182" t="n">
         <v>181</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DR-216</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2.018117268740813</v>
+        <v>2.220289968953771</v>
       </c>
       <c r="D183" t="n">
         <v>182</v>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DR-33</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2.018398240087811</v>
+        <v>2.223119577860926</v>
       </c>
       <c r="D184" t="n">
         <v>183</v>
@@ -3379,11 +3379,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DR-131</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2.026218569728077</v>
+        <v>2.225006573344068</v>
       </c>
       <c r="D185" t="n">
         <v>184</v>
@@ -3395,11 +3395,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SCR-05</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2.02785013471049</v>
+        <v>2.229240414140046</v>
       </c>
       <c r="D186" t="n">
         <v>185</v>
@@ -3411,11 +3411,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DR-129</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2.034685308983355</v>
+        <v>2.230133450801151</v>
       </c>
       <c r="D187" t="n">
         <v>186</v>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DR-21</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2.043188798254071</v>
+        <v>2.231858561121443</v>
       </c>
       <c r="D188" t="n">
         <v>187</v>
@@ -3443,11 +3443,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DR-125</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2.044164042330892</v>
+        <v>2.232821387769613</v>
       </c>
       <c r="D189" t="n">
         <v>188</v>
@@ -3459,11 +3459,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DR-71</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2.046722449898591</v>
+        <v>2.24112536121126</v>
       </c>
       <c r="D190" t="n">
         <v>189</v>
@@ -3475,11 +3475,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DR-32</t>
+          <t>DR-147</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2.049431313331318</v>
+        <v>2.251599629335519</v>
       </c>
       <c r="D191" t="n">
         <v>190</v>
@@ -3491,11 +3491,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DR-130</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2.064521789994401</v>
+        <v>2.252994582958524</v>
       </c>
       <c r="D192" t="n">
         <v>191</v>
@@ -3507,11 +3507,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DR-87</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2.065130085085554</v>
+        <v>2.255892751511583</v>
       </c>
       <c r="D193" t="n">
         <v>192</v>
@@ -3523,11 +3523,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DR-149</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2.072953875779553</v>
+        <v>2.259099035749748</v>
       </c>
       <c r="D194" t="n">
         <v>193</v>
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LSC-10</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2.081002824992755</v>
+        <v>2.260759932563584</v>
       </c>
       <c r="D195" t="n">
         <v>194</v>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DR-165</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2.081316375321893</v>
+        <v>2.261858651996707</v>
       </c>
       <c r="D196" t="n">
         <v>195</v>
@@ -3571,11 +3571,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>LSC-04</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2.083250363831275</v>
+        <v>2.264799225641989</v>
       </c>
       <c r="D197" t="n">
         <v>196</v>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DR-123</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2.084039893130901</v>
+        <v>2.268338648417913</v>
       </c>
       <c r="D198" t="n">
         <v>197</v>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DR-154</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2.085891368262413</v>
+        <v>2.271950175919803</v>
       </c>
       <c r="D199" t="n">
         <v>198</v>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DR-223</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2.086703795324099</v>
+        <v>2.276052670040298</v>
       </c>
       <c r="D200" t="n">
         <v>199</v>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DR-108</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>2.088040329544943</v>
+        <v>2.278242803678034</v>
       </c>
       <c r="D201" t="n">
         <v>200</v>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DR-177</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2.088949971589709</v>
+        <v>2.27836007888273</v>
       </c>
       <c r="D202" t="n">
         <v>201</v>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DR-158</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2.090306596250556</v>
+        <v>2.28102664481476</v>
       </c>
       <c r="D203" t="n">
         <v>202</v>
@@ -3683,11 +3683,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SCR-07</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2.091113044120294</v>
+        <v>2.284764632498061</v>
       </c>
       <c r="D204" t="n">
         <v>203</v>
@@ -3699,11 +3699,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DR-147</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2.094223202697414</v>
+        <v>2.29375712642491</v>
       </c>
       <c r="D205" t="n">
         <v>204</v>
@@ -3715,11 +3715,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DR-215</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2.096483224717089</v>
+        <v>2.296832999158168</v>
       </c>
       <c r="D206" t="n">
         <v>205</v>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SCR-03</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2.10535634101537</v>
+        <v>2.297180758297234</v>
       </c>
       <c r="D207" t="n">
         <v>206</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DR-139</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2.116230317482735</v>
+        <v>2.297444386147679</v>
       </c>
       <c r="D208" t="n">
         <v>207</v>
@@ -3763,11 +3763,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DR-128</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2.11669539454337</v>
+        <v>2.29950991616227</v>
       </c>
       <c r="D209" t="n">
         <v>208</v>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DR-146</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2.120532249548834</v>
+        <v>2.300549263951889</v>
       </c>
       <c r="D210" t="n">
         <v>209</v>
@@ -3795,11 +3795,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DR-171</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2.125722414965174</v>
+        <v>2.307212473484341</v>
       </c>
       <c r="D211" t="n">
         <v>210</v>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DR-136</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2.126749994648585</v>
+        <v>2.307309323277349</v>
       </c>
       <c r="D212" t="n">
         <v>211</v>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>LSC-06</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2.127284864671742</v>
+        <v>2.310078783745527</v>
       </c>
       <c r="D213" t="n">
         <v>212</v>
@@ -3843,11 +3843,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>LSC-65</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2.130772912792541</v>
+        <v>2.312683028332749</v>
       </c>
       <c r="D214" t="n">
         <v>213</v>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DR-109</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2.135546246102705</v>
+        <v>2.314074381837257</v>
       </c>
       <c r="D215" t="n">
         <v>214</v>
@@ -3875,11 +3875,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DR-127</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2.141542948187715</v>
+        <v>2.314202806769955</v>
       </c>
       <c r="D216" t="n">
         <v>215</v>
@@ -3891,11 +3891,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DR-76</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2.148632970839489</v>
+        <v>2.315986402930989</v>
       </c>
       <c r="D217" t="n">
         <v>216</v>
@@ -3907,11 +3907,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DR-132</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2.166148922456403</v>
+        <v>2.322323426211413</v>
       </c>
       <c r="D218" t="n">
         <v>217</v>
@@ -3923,11 +3923,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>LSC-64</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2.172607852869704</v>
+        <v>2.327403876694948</v>
       </c>
       <c r="D219" t="n">
         <v>218</v>
@@ -3939,11 +3939,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DR-95</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2.176647093965513</v>
+        <v>2.32995812816488</v>
       </c>
       <c r="D220" t="n">
         <v>219</v>
@@ -3955,11 +3955,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DR-86</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2.17750024338224</v>
+        <v>2.334162795384354</v>
       </c>
       <c r="D221" t="n">
         <v>220</v>
@@ -3971,11 +3971,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DR-181</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>2.178932884511713</v>
+        <v>2.335539515654354</v>
       </c>
       <c r="D222" t="n">
         <v>221</v>
@@ -3987,11 +3987,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DR-133</t>
+          <t>LSC-64</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>2.190345473003363</v>
+        <v>2.33938430937069</v>
       </c>
       <c r="D223" t="n">
         <v>222</v>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DR-83</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2.19143493912578</v>
+        <v>2.339729446619194</v>
       </c>
       <c r="D224" t="n">
         <v>223</v>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DR-88</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2.203451569486536</v>
+        <v>2.343028867486705</v>
       </c>
       <c r="D225" t="n">
         <v>224</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>LSC-11</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2.203822381661385</v>
+        <v>2.349025270834415</v>
       </c>
       <c r="D226" t="n">
         <v>225</v>
@@ -4051,11 +4051,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DR-112</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>2.204136658833137</v>
+        <v>2.375975907627544</v>
       </c>
       <c r="D227" t="n">
         <v>226</v>
@@ -4067,11 +4067,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DR-46</t>
+          <t>DR-158</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2.204176982354598</v>
+        <v>2.38621374548543</v>
       </c>
       <c r="D228" t="n">
         <v>227</v>
@@ -4083,11 +4083,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DR-31</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2.205737550664038</v>
+        <v>2.388775715883406</v>
       </c>
       <c r="D229" t="n">
         <v>228</v>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>LSC-08</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2.206882229904289</v>
+        <v>2.390491040376088</v>
       </c>
       <c r="D230" t="n">
         <v>229</v>
@@ -4115,11 +4115,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DR-121</t>
+          <t>DR-150</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2.216955541102134</v>
+        <v>2.393539751665371</v>
       </c>
       <c r="D231" t="n">
         <v>230</v>
@@ -4131,11 +4131,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DR-126</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2.223881941993485</v>
+        <v>2.394271567480889</v>
       </c>
       <c r="D232" t="n">
         <v>231</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DR-137</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>2.223896127127902</v>
+        <v>2.39799310308697</v>
       </c>
       <c r="D233" t="n">
         <v>232</v>
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DR-74</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>2.225614607342026</v>
+        <v>2.401034544944717</v>
       </c>
       <c r="D234" t="n">
         <v>233</v>
@@ -4179,11 +4179,11 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>LSC-66</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>2.225831461264398</v>
+        <v>2.410312877005336</v>
       </c>
       <c r="D235" t="n">
         <v>234</v>
@@ -4195,11 +4195,11 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>DR-113</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>2.234670069502203</v>
+        <v>2.422894220482946</v>
       </c>
       <c r="D236" t="n">
         <v>235</v>
@@ -4211,11 +4211,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>DR-228</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2.237827733145832</v>
+        <v>2.425281758528538</v>
       </c>
       <c r="D237" t="n">
         <v>236</v>
@@ -4227,11 +4227,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DR-100</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2.240698464588561</v>
+        <v>2.428525468734927</v>
       </c>
       <c r="D238" t="n">
         <v>237</v>
@@ -4243,11 +4243,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DR-96</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>2.254554424530056</v>
+        <v>2.428881621998821</v>
       </c>
       <c r="D239" t="n">
         <v>238</v>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DR-58</t>
+          <t>LSC-67</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2.255412267271748</v>
+        <v>2.441987159513681</v>
       </c>
       <c r="D240" t="n">
         <v>239</v>
@@ -4275,11 +4275,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DR-104</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>2.255460955039642</v>
+        <v>2.448805463228918</v>
       </c>
       <c r="D241" t="n">
         <v>240</v>
@@ -4291,11 +4291,11 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>LSC-67</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2.256684013059453</v>
+        <v>2.452018329269186</v>
       </c>
       <c r="D242" t="n">
         <v>241</v>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DR-214</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>2.257114407720129</v>
+        <v>2.461625801510433</v>
       </c>
       <c r="D243" t="n">
         <v>242</v>
@@ -4323,11 +4323,11 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DR-07</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>2.259617052322659</v>
+        <v>2.482105094638149</v>
       </c>
       <c r="D244" t="n">
         <v>243</v>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>DR-107</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>2.259665662626821</v>
+        <v>2.499528198209817</v>
       </c>
       <c r="D245" t="n">
         <v>244</v>
@@ -4355,11 +4355,11 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>LSC-13</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>2.266317888729191</v>
+        <v>2.500557496405967</v>
       </c>
       <c r="D246" t="n">
         <v>245</v>
@@ -4371,11 +4371,11 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DR-97</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>2.274104618603809</v>
+        <v>2.508492250337581</v>
       </c>
       <c r="D247" t="n">
         <v>246</v>
@@ -4387,11 +4387,11 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>DR-62</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>2.282875574279874</v>
+        <v>2.522424185332514</v>
       </c>
       <c r="D248" t="n">
         <v>247</v>
@@ -4403,11 +4403,11 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DR-229</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>2.284128560208866</v>
+        <v>2.525082203622054</v>
       </c>
       <c r="D249" t="n">
         <v>248</v>
@@ -4419,11 +4419,11 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DR-220</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2.292223632375156</v>
+        <v>2.525419265869063</v>
       </c>
       <c r="D250" t="n">
         <v>249</v>
@@ -4435,11 +4435,11 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DR-34</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2.292972393683529</v>
+        <v>2.52557202971079</v>
       </c>
       <c r="D251" t="n">
         <v>250</v>
@@ -4451,11 +4451,11 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DR-61</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2.296875612013175</v>
+        <v>2.530676486042497</v>
       </c>
       <c r="D252" t="n">
         <v>251</v>
@@ -4467,11 +4467,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DR-93</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2.297143345271413</v>
+        <v>2.565259693642644</v>
       </c>
       <c r="D253" t="n">
         <v>252</v>
@@ -4483,11 +4483,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DR-105</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>2.30436021976333</v>
+        <v>2.595358736687656</v>
       </c>
       <c r="D254" t="n">
         <v>253</v>
@@ -4499,11 +4499,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DR-63</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>2.30486265002722</v>
+        <v>2.604400927005964</v>
       </c>
       <c r="D255" t="n">
         <v>254</v>
@@ -4515,11 +4515,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DR-180</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>2.3080956171541</v>
+        <v>2.615777777329704</v>
       </c>
       <c r="D256" t="n">
         <v>255</v>
@@ -4531,11 +4531,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DR-13</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>2.313208908872125</v>
+        <v>2.624971857590104</v>
       </c>
       <c r="D257" t="n">
         <v>256</v>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DR-212</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>2.314180477869079</v>
+        <v>2.638571662726907</v>
       </c>
       <c r="D258" t="n">
         <v>257</v>
@@ -4563,11 +4563,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DR-91</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>2.316945052472657</v>
+        <v>2.639369934510249</v>
       </c>
       <c r="D259" t="n">
         <v>258</v>
@@ -4579,11 +4579,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DR-77</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2.318957803555949</v>
+        <v>2.646428840417316</v>
       </c>
       <c r="D260" t="n">
         <v>259</v>
@@ -4595,11 +4595,11 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DR-221</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>2.330870386706418</v>
+        <v>2.648162981822662</v>
       </c>
       <c r="D261" t="n">
         <v>260</v>
@@ -4611,11 +4611,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DR-90</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>2.335668552758849</v>
+        <v>2.655430967516265</v>
       </c>
       <c r="D262" t="n">
         <v>261</v>
@@ -4627,11 +4627,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DR-219</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>2.346199314269018</v>
+        <v>2.656066814950067</v>
       </c>
       <c r="D263" t="n">
         <v>262</v>
@@ -4643,11 +4643,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DR-101</t>
+          <t>LSC-21</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>2.348258009303215</v>
+        <v>2.672903602278086</v>
       </c>
       <c r="D264" t="n">
         <v>263</v>
@@ -4659,11 +4659,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DR-82</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2.348721230239666</v>
+        <v>2.689031481373263</v>
       </c>
       <c r="D265" t="n">
         <v>264</v>
@@ -4675,11 +4675,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DR-89</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2.351987073613496</v>
+        <v>2.702709315146848</v>
       </c>
       <c r="D266" t="n">
         <v>265</v>
@@ -4691,11 +4691,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DR-67</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2.358760136520586</v>
+        <v>2.737962014058381</v>
       </c>
       <c r="D267" t="n">
         <v>266</v>
@@ -4707,11 +4707,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DR-102</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2.359783330369048</v>
+        <v>2.742880129778849</v>
       </c>
       <c r="D268" t="n">
         <v>267</v>
@@ -4723,11 +4723,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DR-69</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>2.36314673404761</v>
+        <v>2.748875610260198</v>
       </c>
       <c r="D269" t="n">
         <v>268</v>
@@ -4739,11 +4739,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DR-116</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2.36703624029589</v>
+        <v>2.755765981286671</v>
       </c>
       <c r="D270" t="n">
         <v>269</v>
@@ -4755,11 +4755,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>LSC-21</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>2.368060561585506</v>
+        <v>2.768738176094477</v>
       </c>
       <c r="D271" t="n">
         <v>270</v>
@@ -4771,11 +4771,11 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DR-68</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>2.372058461372703</v>
+        <v>2.770681304793961</v>
       </c>
       <c r="D272" t="n">
         <v>271</v>
@@ -4787,11 +4787,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DR-75</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2.374953150857532</v>
+        <v>2.777213482486818</v>
       </c>
       <c r="D273" t="n">
         <v>272</v>
@@ -4803,11 +4803,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DR-99</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2.376235026414684</v>
+        <v>2.779662737567769</v>
       </c>
       <c r="D274" t="n">
         <v>273</v>
@@ -4819,11 +4819,11 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DR-135</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>2.38494398826685</v>
+        <v>2.780198093405286</v>
       </c>
       <c r="D275" t="n">
         <v>274</v>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DR-02</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2.39194196653103</v>
+        <v>2.804543227225618</v>
       </c>
       <c r="D276" t="n">
         <v>275</v>
@@ -4851,11 +4851,11 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DR-161</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2.393590691441895</v>
+        <v>2.806161287772997</v>
       </c>
       <c r="D277" t="n">
         <v>276</v>
@@ -4867,11 +4867,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DR-117</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2.396016929997975</v>
+        <v>2.828110731461255</v>
       </c>
       <c r="D278" t="n">
         <v>277</v>
@@ -4883,11 +4883,11 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DR-66</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>2.397511512949263</v>
+        <v>2.828337134406274</v>
       </c>
       <c r="D279" t="n">
         <v>278</v>
@@ -4899,11 +4899,11 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DR-124</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2.401502497806764</v>
+        <v>2.835883522702789</v>
       </c>
       <c r="D280" t="n">
         <v>279</v>
@@ -4915,11 +4915,11 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DR-78</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2.405839589865746</v>
+        <v>2.848128845937355</v>
       </c>
       <c r="D281" t="n">
         <v>280</v>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DR-134</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2.4168979905181</v>
+        <v>2.849106114375117</v>
       </c>
       <c r="D282" t="n">
         <v>281</v>
@@ -4947,11 +4947,11 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DR-122</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>2.422787695365836</v>
+        <v>2.856229436316573</v>
       </c>
       <c r="D283" t="n">
         <v>282</v>
@@ -4963,11 +4963,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DR-213</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2.426771971913964</v>
+        <v>2.86308990817016</v>
       </c>
       <c r="D284" t="n">
         <v>283</v>
@@ -4979,11 +4979,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DR-211</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2.428814020697357</v>
+        <v>2.891496686576744</v>
       </c>
       <c r="D285" t="n">
         <v>284</v>
@@ -4995,11 +4995,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DR-114</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>2.4423036152023</v>
+        <v>2.897048071644897</v>
       </c>
       <c r="D286" t="n">
         <v>285</v>
@@ -5011,11 +5011,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DR-224</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2.452432568727802</v>
+        <v>2.927468349376309</v>
       </c>
       <c r="D287" t="n">
         <v>286</v>
@@ -5027,11 +5027,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DR-72</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2.453079648755606</v>
+        <v>2.946061666972061</v>
       </c>
       <c r="D288" t="n">
         <v>287</v>
@@ -5043,11 +5043,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DR-92</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2.453571057280282</v>
+        <v>2.955276723199473</v>
       </c>
       <c r="D289" t="n">
         <v>288</v>
@@ -5059,11 +5059,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DR-210</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2.454169640740191</v>
+        <v>2.964881917860374</v>
       </c>
       <c r="D290" t="n">
         <v>289</v>
@@ -5075,11 +5075,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DR-187</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2.457863055672472</v>
+        <v>3.005732969819836</v>
       </c>
       <c r="D291" t="n">
         <v>290</v>
@@ -5091,11 +5091,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>DR-190</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2.470978398980838</v>
+        <v>3.017398639888179</v>
       </c>
       <c r="D292" t="n">
         <v>291</v>
@@ -5107,11 +5107,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DR-217</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2.480516179683955</v>
+        <v>3.018043803033257</v>
       </c>
       <c r="D293" t="n">
         <v>292</v>
@@ -5123,11 +5123,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DR-79</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2.490232968012455</v>
+        <v>3.024836256981411</v>
       </c>
       <c r="D294" t="n">
         <v>293</v>
@@ -5139,11 +5139,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DR-106</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2.492312144090535</v>
+        <v>3.034834106401724</v>
       </c>
       <c r="D295" t="n">
         <v>294</v>
@@ -5155,11 +5155,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DR-234</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>2.519171985976699</v>
+        <v>3.038434108434989</v>
       </c>
       <c r="D296" t="n">
         <v>295</v>
@@ -5171,11 +5171,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DR-120</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2.524351354525623</v>
+        <v>3.059992957472789</v>
       </c>
       <c r="D297" t="n">
         <v>296</v>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DR-218</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>2.529428290251174</v>
+        <v>3.073047174998289</v>
       </c>
       <c r="D298" t="n">
         <v>297</v>
@@ -5203,11 +5203,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DR-115</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2.547750144832546</v>
+        <v>3.099881717549489</v>
       </c>
       <c r="D299" t="n">
         <v>298</v>
@@ -5219,11 +5219,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DR-118</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2.579469130443514</v>
+        <v>3.134777259727415</v>
       </c>
       <c r="D300" t="n">
         <v>299</v>
@@ -5235,11 +5235,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DR-60</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2.584000025092682</v>
+        <v>3.197565044098575</v>
       </c>
       <c r="D301" t="n">
         <v>300</v>
@@ -5251,11 +5251,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>DR-06</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2.605927234642048</v>
+        <v>3.198662092503117</v>
       </c>
       <c r="D302" t="n">
         <v>301</v>
@@ -5267,11 +5267,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>DR-119</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2.62024303491666</v>
+        <v>3.216209488787511</v>
       </c>
       <c r="D303" t="n">
         <v>302</v>
@@ -5283,11 +5283,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DR-73</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2.621194705301892</v>
+        <v>3.290935766597475</v>
       </c>
       <c r="D304" t="n">
         <v>303</v>
@@ -5299,11 +5299,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DR-81</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2.624215029366092</v>
+        <v>3.30692977699704</v>
       </c>
       <c r="D305" t="n">
         <v>304</v>
@@ -5315,11 +5315,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DR-84</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2.640653492217719</v>
+        <v>3.309041928467221</v>
       </c>
       <c r="D306" t="n">
         <v>305</v>
@@ -5331,11 +5331,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DR-111</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>2.703076605509886</v>
+        <v>3.365758691725556</v>
       </c>
       <c r="D307" t="n">
         <v>306</v>
@@ -5347,11 +5347,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DR-70</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2.7795796897841</v>
+        <v>3.448611406782728</v>
       </c>
       <c r="D308" t="n">
         <v>307</v>
@@ -5363,11 +5363,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DR-64</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2.787062342419811</v>
+        <v>3.466966330958262</v>
       </c>
       <c r="D309" t="n">
         <v>308</v>
@@ -5379,11 +5379,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DR-80</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2.8140454359108</v>
+        <v>3.634261841943198</v>
       </c>
       <c r="D310" t="n">
         <v>309</v>
@@ -5395,11 +5395,11 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DR-138</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2.922053110669861</v>
+        <v>3.843072954416419</v>
       </c>
       <c r="D311" t="n">
         <v>310</v>
